--- a/research/traditional_assets/database/data/oman/oman_engineering_construction.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_engineering_construction.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1053964768340021</v>
+        <v>0.1052766321187511</v>
       </c>
       <c r="C2">
-        <v>347.7806659668493</v>
+        <v>345.3459603003786</v>
       </c>
       <c r="D2">
-        <v>315.7806659668493</v>
+        <v>316.4169603003787</v>
       </c>
       <c r="E2">
-        <v>-261.1</v>
+        <v>-258.029</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.071</v>
       </c>
       <c r="G2">
         <v>32</v>
@@ -1579,28 +1579,28 @@
         <v>18.99</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1544713</v>
       </c>
       <c r="N2">
-        <v>18.99</v>
+        <v>18.8355287</v>
       </c>
       <c r="O2">
-        <v>2.8485</v>
+        <v>2.825329305</v>
       </c>
       <c r="P2">
-        <v>16.1415</v>
+        <v>16.010199395</v>
       </c>
       <c r="Q2">
-        <v>19.9515</v>
+        <v>19.820199395</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1053964768340021</v>
+        <v>0.1059081637563142</v>
       </c>
       <c r="T2">
-        <v>0.7767418785034673</v>
+        <v>0.7834108744300121</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>122.9354579135412</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1052766321187511</v>
+        <v>0.1051567874035001</v>
       </c>
       <c r="C3">
-        <v>345.3459603003786</v>
+        <v>342.9138240624957</v>
       </c>
       <c r="D3">
-        <v>316.4169603003787</v>
+        <v>317.0558240624957</v>
       </c>
       <c r="E3">
-        <v>-258.029</v>
+        <v>-254.958</v>
       </c>
       <c r="F3">
-        <v>3.071</v>
+        <v>6.142</v>
       </c>
       <c r="G3">
         <v>32</v>
@@ -1661,28 +1661,28 @@
         <v>18.99</v>
       </c>
       <c r="M3">
-        <v>0.1544713</v>
+        <v>0.3089426</v>
       </c>
       <c r="N3">
-        <v>18.8355287</v>
+        <v>18.6810574</v>
       </c>
       <c r="O3">
-        <v>2.825329305</v>
+        <v>2.80215861</v>
       </c>
       <c r="P3">
-        <v>16.010199395</v>
+        <v>15.87889879</v>
       </c>
       <c r="Q3">
-        <v>19.820199395</v>
+        <v>19.68889879</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1059081637563142</v>
+        <v>0.1064302932688777</v>
       </c>
       <c r="T3">
-        <v>0.7834108744300121</v>
+        <v>0.7902159723142418</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>122.9354579135412</v>
+        <v>61.46772895677061</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1051567874035001</v>
+        <v>0.1050369426882491</v>
       </c>
       <c r="C4">
-        <v>342.9138240624957</v>
+        <v>340.4842728481534</v>
       </c>
       <c r="D4">
-        <v>317.0558240624957</v>
+        <v>317.6972728481534</v>
       </c>
       <c r="E4">
-        <v>-254.958</v>
+        <v>-251.887</v>
       </c>
       <c r="F4">
-        <v>6.142</v>
+        <v>9.213000000000001</v>
       </c>
       <c r="G4">
         <v>32</v>
@@ -1743,28 +1743,28 @@
         <v>18.99</v>
       </c>
       <c r="M4">
-        <v>0.3089426</v>
+        <v>0.4634139</v>
       </c>
       <c r="N4">
-        <v>18.6810574</v>
+        <v>18.5265861</v>
       </c>
       <c r="O4">
-        <v>2.80215861</v>
+        <v>2.778987915000001</v>
       </c>
       <c r="P4">
-        <v>15.87889879</v>
+        <v>15.747598185</v>
       </c>
       <c r="Q4">
-        <v>19.68889879</v>
+        <v>19.557598185</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1064302932688777</v>
+        <v>0.1069631883384011</v>
       </c>
       <c r="T4">
-        <v>0.7902159723142418</v>
+        <v>0.7971613814950532</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>61.46772895677061</v>
+        <v>40.97848597118041</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1050369426882491</v>
+        <v>0.1049170979729981</v>
       </c>
       <c r="C5">
-        <v>340.4842728481534</v>
+        <v>338.0573223787628</v>
       </c>
       <c r="D5">
-        <v>317.6972728481534</v>
+        <v>318.3413223787628</v>
       </c>
       <c r="E5">
-        <v>-251.887</v>
+        <v>-248.816</v>
       </c>
       <c r="F5">
-        <v>9.213000000000001</v>
+        <v>12.284</v>
       </c>
       <c r="G5">
         <v>32</v>
@@ -1825,28 +1825,28 @@
         <v>18.99</v>
       </c>
       <c r="M5">
-        <v>0.4634139</v>
+        <v>0.6178852</v>
       </c>
       <c r="N5">
-        <v>18.5265861</v>
+        <v>18.3721148</v>
       </c>
       <c r="O5">
-        <v>2.778987915000001</v>
+        <v>2.75581722</v>
       </c>
       <c r="P5">
-        <v>15.747598185</v>
+        <v>15.61629758</v>
       </c>
       <c r="Q5">
-        <v>19.557598185</v>
+        <v>19.42629758</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1069631883384011</v>
+        <v>0.1075071853885397</v>
       </c>
       <c r="T5">
-        <v>0.7971613814950532</v>
+        <v>0.8042514867004651</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>40.97848597118041</v>
+        <v>30.73386447838531</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1049170979729981</v>
+        <v>0.1047972532577471</v>
       </c>
       <c r="C6">
-        <v>338.0573223787628</v>
+        <v>335.6329885034793</v>
       </c>
       <c r="D6">
-        <v>318.3413223787628</v>
+        <v>318.9879885034794</v>
       </c>
       <c r="E6">
-        <v>-248.816</v>
+        <v>-245.745</v>
       </c>
       <c r="F6">
-        <v>12.284</v>
+        <v>15.355</v>
       </c>
       <c r="G6">
         <v>32</v>
@@ -1907,28 +1907,28 @@
         <v>18.99</v>
       </c>
       <c r="M6">
-        <v>0.6178852</v>
+        <v>0.7723565000000001</v>
       </c>
       <c r="N6">
-        <v>18.3721148</v>
+        <v>18.2176435</v>
       </c>
       <c r="O6">
-        <v>2.75581722</v>
+        <v>2.732646525</v>
       </c>
       <c r="P6">
-        <v>15.61629758</v>
+        <v>15.484996975</v>
       </c>
       <c r="Q6">
-        <v>19.42629758</v>
+        <v>19.294996975</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1075071853885397</v>
+        <v>0.1080626350081548</v>
       </c>
       <c r="T6">
-        <v>0.8042514867004651</v>
+        <v>0.8114908572786225</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>30.73386447838531</v>
+        <v>24.58709158270824</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1047972532577471</v>
+        <v>0.1046774085424961</v>
       </c>
       <c r="C7">
-        <v>335.6329885034793</v>
+        <v>333.2112872005016</v>
       </c>
       <c r="D7">
-        <v>318.9879885034794</v>
+        <v>319.6372872005016</v>
       </c>
       <c r="E7">
-        <v>-245.745</v>
+        <v>-242.674</v>
       </c>
       <c r="F7">
-        <v>15.355</v>
+        <v>18.426</v>
       </c>
       <c r="G7">
         <v>32</v>
@@ -1989,28 +1989,28 @@
         <v>18.99</v>
       </c>
       <c r="M7">
-        <v>0.7723565000000001</v>
+        <v>0.9268278000000001</v>
       </c>
       <c r="N7">
-        <v>18.2176435</v>
+        <v>18.0631722</v>
       </c>
       <c r="O7">
-        <v>2.732646525</v>
+        <v>2.70947583</v>
       </c>
       <c r="P7">
-        <v>15.484996975</v>
+        <v>15.35369637</v>
       </c>
       <c r="Q7">
-        <v>19.294996975</v>
+        <v>19.16369637</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1080626350081548</v>
+        <v>0.1086299027047831</v>
       </c>
       <c r="T7">
-        <v>0.8114908572786225</v>
+        <v>0.8188842570180171</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.58709158270824</v>
+        <v>20.4892429855902</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1046774085424961</v>
+        <v>0.1045575638272451</v>
       </c>
       <c r="C8">
-        <v>333.2112872005017</v>
+        <v>330.7922345783877</v>
       </c>
       <c r="D8">
-        <v>319.6372872005016</v>
+        <v>320.2892345783877</v>
       </c>
       <c r="E8">
-        <v>-242.674</v>
+        <v>-239.603</v>
       </c>
       <c r="F8">
-        <v>18.426</v>
+        <v>21.497</v>
       </c>
       <c r="G8">
         <v>32</v>
@@ -2071,28 +2071,28 @@
         <v>18.99</v>
       </c>
       <c r="M8">
-        <v>0.9268278000000001</v>
+        <v>1.0812991</v>
       </c>
       <c r="N8">
-        <v>18.0631722</v>
+        <v>17.9087009</v>
       </c>
       <c r="O8">
-        <v>2.70947583</v>
+        <v>2.686305135</v>
       </c>
       <c r="P8">
-        <v>15.35369637</v>
+        <v>15.222395765</v>
       </c>
       <c r="Q8">
-        <v>19.16369637</v>
+        <v>19.032395765</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1086299027047831</v>
+        <v>0.1092093697067151</v>
       </c>
       <c r="T8">
-        <v>0.8188842570180171</v>
+        <v>0.8264366546012698</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.4892429855902</v>
+        <v>17.56220827336304</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1045575638272451</v>
+        <v>0.1044377191119941</v>
       </c>
       <c r="C9">
-        <v>330.7922345783878</v>
+        <v>328.3758468773876</v>
       </c>
       <c r="D9">
-        <v>320.2892345783878</v>
+        <v>320.9438468773876</v>
       </c>
       <c r="E9">
-        <v>-239.603</v>
+        <v>-236.532</v>
       </c>
       <c r="F9">
-        <v>21.497</v>
+        <v>24.568</v>
       </c>
       <c r="G9">
         <v>32</v>
@@ -2153,28 +2153,28 @@
         <v>18.99</v>
       </c>
       <c r="M9">
-        <v>1.0812991</v>
+        <v>1.2357704</v>
       </c>
       <c r="N9">
-        <v>17.9087009</v>
+        <v>17.7542296</v>
       </c>
       <c r="O9">
-        <v>2.686305135</v>
+        <v>2.66313444</v>
       </c>
       <c r="P9">
-        <v>15.222395765</v>
+        <v>15.09109516</v>
       </c>
       <c r="Q9">
-        <v>19.032395765</v>
+        <v>18.90109516</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1092093697067151</v>
+        <v>0.1098014338173849</v>
       </c>
       <c r="T9">
-        <v>0.8264366546012698</v>
+        <v>0.8341532347406801</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.56220827336303</v>
+        <v>15.36693223919265</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1044377191119941</v>
+        <v>0.1043178743967431</v>
       </c>
       <c r="C10">
-        <v>328.3758468773876</v>
+        <v>325.9621404707913</v>
       </c>
       <c r="D10">
-        <v>320.9438468773876</v>
+        <v>321.6011404707913</v>
       </c>
       <c r="E10">
-        <v>-236.532</v>
+        <v>-233.461</v>
       </c>
       <c r="F10">
-        <v>24.568</v>
+        <v>27.639</v>
       </c>
       <c r="G10">
         <v>32</v>
@@ -2235,28 +2235,28 @@
         <v>18.99</v>
       </c>
       <c r="M10">
-        <v>1.2357704</v>
+        <v>1.3902417</v>
       </c>
       <c r="N10">
-        <v>17.7542296</v>
+        <v>17.5997583</v>
       </c>
       <c r="O10">
-        <v>2.66313444</v>
+        <v>2.639963745</v>
       </c>
       <c r="P10">
-        <v>15.09109516</v>
+        <v>14.959794555</v>
       </c>
       <c r="Q10">
-        <v>18.90109516</v>
+        <v>18.769794555</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1098014338173849</v>
+        <v>0.1104065103260913</v>
       </c>
       <c r="T10">
-        <v>0.8341532347406801</v>
+        <v>0.8420394100479895</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.36693223919265</v>
+        <v>13.65949532372681</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1043178743967431</v>
+        <v>0.1043255296814921</v>
       </c>
       <c r="C11">
-        <v>325.9621404707913</v>
+        <v>322.84907424227</v>
       </c>
       <c r="D11">
-        <v>321.6011404707913</v>
+        <v>321.55907424227</v>
       </c>
       <c r="E11">
-        <v>-233.461</v>
+        <v>-230.39</v>
       </c>
       <c r="F11">
-        <v>27.639</v>
+        <v>30.71</v>
       </c>
       <c r="G11">
         <v>32</v>
@@ -2317,45 +2317,45 @@
         <v>18.99</v>
       </c>
       <c r="M11">
-        <v>1.3902417</v>
+        <v>1.590778</v>
       </c>
       <c r="N11">
-        <v>17.5997583</v>
+        <v>17.399222</v>
       </c>
       <c r="O11">
-        <v>2.639963745</v>
+        <v>2.6098833</v>
       </c>
       <c r="P11">
-        <v>14.959794555</v>
+        <v>14.7893387</v>
       </c>
       <c r="Q11">
-        <v>18.769794555</v>
+        <v>18.5993387</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1104065103260913</v>
+        <v>0.1110250329794356</v>
       </c>
       <c r="T11">
-        <v>0.8420394100479895</v>
+        <v>0.8501008336954615</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.15</v>
       </c>
       <c r="W11">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.65949532372681</v>
+        <v>11.93755508311028</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1043255296814921</v>
+        <v>0.1042184349662411</v>
       </c>
       <c r="C12">
-        <v>322.84907424227</v>
+        <v>320.3675675676605</v>
       </c>
       <c r="D12">
-        <v>321.55907424227</v>
+        <v>322.1485675676605</v>
       </c>
       <c r="E12">
-        <v>-230.39</v>
+        <v>-227.319</v>
       </c>
       <c r="F12">
-        <v>30.71</v>
+        <v>33.78100000000001</v>
       </c>
       <c r="G12">
         <v>32</v>
@@ -2399,28 +2399,28 @@
         <v>18.99</v>
       </c>
       <c r="M12">
-        <v>1.590778</v>
+        <v>1.7498558</v>
       </c>
       <c r="N12">
-        <v>17.399222</v>
+        <v>17.2401442</v>
       </c>
       <c r="O12">
-        <v>2.6098833</v>
+        <v>2.58602163</v>
       </c>
       <c r="P12">
-        <v>14.7893387</v>
+        <v>14.65412257</v>
       </c>
       <c r="Q12">
-        <v>18.5993387</v>
+        <v>18.46412257</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1110250329794356</v>
+        <v>0.1116574550182484</v>
       </c>
       <c r="T12">
-        <v>0.8501008336954615</v>
+        <v>0.858343412930517</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.93755508311028</v>
+        <v>10.85232280282752</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1042184349662411</v>
+        <v>0.1041113402509901</v>
       </c>
       <c r="C13">
-        <v>320.3675675676605</v>
+        <v>317.8882262221122</v>
       </c>
       <c r="D13">
-        <v>322.1485675676605</v>
+        <v>322.7402262221121</v>
       </c>
       <c r="E13">
-        <v>-227.319</v>
+        <v>-224.248</v>
       </c>
       <c r="F13">
-        <v>33.78100000000001</v>
+        <v>36.852</v>
       </c>
       <c r="G13">
         <v>32</v>
@@ -2481,28 +2481,28 @@
         <v>18.99</v>
       </c>
       <c r="M13">
-        <v>1.7498558</v>
+        <v>1.9089336</v>
       </c>
       <c r="N13">
-        <v>17.2401442</v>
+        <v>17.0810664</v>
       </c>
       <c r="O13">
-        <v>2.58602163</v>
+        <v>2.56215996</v>
       </c>
       <c r="P13">
-        <v>14.65412257</v>
+        <v>14.51890644</v>
       </c>
       <c r="Q13">
-        <v>18.46412257</v>
+        <v>18.32890644</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1116574550182484</v>
+        <v>0.112304250285216</v>
       </c>
       <c r="T13">
-        <v>0.858343412930517</v>
+        <v>0.8667733235118238</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.85232280282752</v>
+        <v>9.947962569258564</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1041113402509901</v>
+        <v>0.104192095535739</v>
       </c>
       <c r="C14">
-        <v>317.8882262221122</v>
+        <v>314.3708819244912</v>
       </c>
       <c r="D14">
-        <v>322.7402262221121</v>
+        <v>322.2938819244912</v>
       </c>
       <c r="E14">
-        <v>-224.248</v>
+        <v>-221.177</v>
       </c>
       <c r="F14">
-        <v>36.852</v>
+        <v>39.923</v>
       </c>
       <c r="G14">
         <v>32</v>
@@ -2563,45 +2563,45 @@
         <v>18.99</v>
       </c>
       <c r="M14">
-        <v>1.9089336</v>
+        <v>2.1358805</v>
       </c>
       <c r="N14">
-        <v>17.0810664</v>
+        <v>16.8541195</v>
       </c>
       <c r="O14">
-        <v>2.56215996</v>
+        <v>2.528117925000001</v>
       </c>
       <c r="P14">
-        <v>14.51890644</v>
+        <v>14.326001575</v>
       </c>
       <c r="Q14">
-        <v>18.32890644</v>
+        <v>18.136001575</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.112304250285216</v>
+        <v>0.1129659144088955</v>
       </c>
       <c r="T14">
-        <v>0.8667733235118238</v>
+        <v>0.8753970251409766</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.15</v>
       </c>
       <c r="W14">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>9.947962569258564</v>
+        <v>8.890946848384075</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.104192095535739</v>
+        <v>0.104099450820488</v>
       </c>
       <c r="C15">
-        <v>314.3708819244912</v>
+        <v>311.8120449808804</v>
       </c>
       <c r="D15">
-        <v>322.2938819244912</v>
+        <v>322.8060449808804</v>
       </c>
       <c r="E15">
-        <v>-221.177</v>
+        <v>-218.106</v>
       </c>
       <c r="F15">
-        <v>39.923</v>
+        <v>42.99400000000001</v>
       </c>
       <c r="G15">
         <v>32</v>
@@ -2645,28 +2645,28 @@
         <v>18.99</v>
       </c>
       <c r="M15">
-        <v>2.1358805</v>
+        <v>2.300179</v>
       </c>
       <c r="N15">
-        <v>16.8541195</v>
+        <v>16.689821</v>
       </c>
       <c r="O15">
-        <v>2.528117925000001</v>
+        <v>2.50347315</v>
       </c>
       <c r="P15">
-        <v>14.326001575</v>
+        <v>14.18634785</v>
       </c>
       <c r="Q15">
-        <v>18.136001575</v>
+        <v>17.99634785</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1129659144088955</v>
+        <v>0.1136429660703349</v>
       </c>
       <c r="T15">
-        <v>0.8753970251409766</v>
+        <v>0.8842212779708075</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.890946848384075</v>
+        <v>8.255879216356639</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.104099450820488</v>
+        <v>0.104006806105237</v>
       </c>
       <c r="C16">
-        <v>311.8120449808804</v>
+        <v>309.254838403328</v>
       </c>
       <c r="D16">
-        <v>322.8060449808804</v>
+        <v>323.319838403328</v>
       </c>
       <c r="E16">
-        <v>-218.106</v>
+        <v>-215.035</v>
       </c>
       <c r="F16">
-        <v>42.99400000000001</v>
+        <v>46.06500000000001</v>
       </c>
       <c r="G16">
         <v>32</v>
@@ -2727,28 +2727,28 @@
         <v>18.99</v>
       </c>
       <c r="M16">
-        <v>2.300179</v>
+        <v>2.464477500000001</v>
       </c>
       <c r="N16">
-        <v>16.689821</v>
+        <v>16.5255225</v>
       </c>
       <c r="O16">
-        <v>2.50347315</v>
+        <v>2.478828375</v>
       </c>
       <c r="P16">
-        <v>14.18634785</v>
+        <v>14.046694125</v>
       </c>
       <c r="Q16">
-        <v>17.99634785</v>
+        <v>17.856694125</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1136429660703349</v>
+        <v>0.1143359483591024</v>
       </c>
       <c r="T16">
-        <v>0.8842212779708075</v>
+        <v>0.8932531602789874</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.255879216356639</v>
+        <v>7.70548726859953</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.104006806105237</v>
+        <v>0.104022961389986</v>
       </c>
       <c r="C17">
-        <v>309.254838403328</v>
+        <v>306.0941259611968</v>
       </c>
       <c r="D17">
-        <v>323.319838403328</v>
+        <v>323.2301259611968</v>
       </c>
       <c r="E17">
-        <v>-215.035</v>
+        <v>-211.964</v>
       </c>
       <c r="F17">
-        <v>46.065</v>
+        <v>49.136</v>
       </c>
       <c r="G17">
         <v>32</v>
@@ -2809,45 +2809,45 @@
         <v>18.99</v>
       </c>
       <c r="M17">
-        <v>2.4644775</v>
+        <v>2.6680848</v>
       </c>
       <c r="N17">
-        <v>16.5255225</v>
+        <v>16.3219152</v>
       </c>
       <c r="O17">
-        <v>2.478828375</v>
+        <v>2.44828728</v>
       </c>
       <c r="P17">
-        <v>14.046694125</v>
+        <v>13.87362792</v>
       </c>
       <c r="Q17">
-        <v>17.856694125</v>
+        <v>17.68362792</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1143359483591024</v>
+        <v>0.1150454302261739</v>
       </c>
       <c r="T17">
-        <v>0.8932531602789874</v>
+        <v>0.9025000874040288</v>
       </c>
       <c r="U17">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.15</v>
       </c>
       <c r="W17">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>7.705487268599531</v>
+        <v>7.117464932149083</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.104022961389986</v>
+        <v>0.103937116674735</v>
       </c>
       <c r="C18">
-        <v>306.0941259611968</v>
+        <v>303.5004045004634</v>
       </c>
       <c r="D18">
-        <v>323.2301259611968</v>
+        <v>323.7074045004634</v>
       </c>
       <c r="E18">
-        <v>-211.964</v>
+        <v>-208.893</v>
       </c>
       <c r="F18">
-        <v>49.136</v>
+        <v>52.20700000000001</v>
       </c>
       <c r="G18">
         <v>32</v>
@@ -2891,28 +2891,28 @@
         <v>18.99</v>
       </c>
       <c r="M18">
-        <v>2.6680848</v>
+        <v>2.834840100000001</v>
       </c>
       <c r="N18">
-        <v>16.3219152</v>
+        <v>16.1551599</v>
       </c>
       <c r="O18">
-        <v>2.44828728</v>
+        <v>2.423273985</v>
       </c>
       <c r="P18">
-        <v>13.87362792</v>
+        <v>13.731885915</v>
       </c>
       <c r="Q18">
-        <v>17.68362792</v>
+        <v>17.541885915</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1150454302261739</v>
+        <v>0.1157720080418495</v>
       </c>
       <c r="T18">
-        <v>0.9025000874040288</v>
+        <v>0.9119698320501552</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.117464932149083</v>
+        <v>6.698790524375607</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.103937116674735</v>
+        <v>0.103851271959484</v>
       </c>
       <c r="C19">
-        <v>303.5004045004634</v>
+        <v>300.9080946139784</v>
       </c>
       <c r="D19">
-        <v>323.7074045004634</v>
+        <v>324.1860946139785</v>
       </c>
       <c r="E19">
-        <v>-208.893</v>
+        <v>-205.822</v>
       </c>
       <c r="F19">
-        <v>52.20700000000001</v>
+        <v>55.27800000000001</v>
       </c>
       <c r="G19">
         <v>32</v>
@@ -2973,28 +2973,28 @@
         <v>18.99</v>
       </c>
       <c r="M19">
-        <v>2.834840100000001</v>
+        <v>3.001595400000001</v>
       </c>
       <c r="N19">
-        <v>16.1551599</v>
+        <v>15.9884046</v>
       </c>
       <c r="O19">
-        <v>2.423273985</v>
+        <v>2.39826069</v>
       </c>
       <c r="P19">
-        <v>13.731885915</v>
+        <v>13.59014391</v>
       </c>
       <c r="Q19">
-        <v>17.541885915</v>
+        <v>17.40014391</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1157720080418495</v>
+        <v>0.1165163072676635</v>
       </c>
       <c r="T19">
-        <v>0.9119698320501552</v>
+        <v>0.9216705460778947</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.698790524375607</v>
+        <v>6.326635495243629</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.103851271959484</v>
+        <v>0.103926927244233</v>
       </c>
       <c r="C20">
-        <v>300.9080946139784</v>
+        <v>297.4151491841671</v>
       </c>
       <c r="D20">
-        <v>324.1860946139785</v>
+        <v>323.7641491841671</v>
       </c>
       <c r="E20">
-        <v>-205.822</v>
+        <v>-202.751</v>
       </c>
       <c r="F20">
-        <v>55.278</v>
+        <v>58.349</v>
       </c>
       <c r="G20">
         <v>32</v>
@@ -3055,45 +3055,45 @@
         <v>18.99</v>
       </c>
       <c r="M20">
-        <v>3.0015954</v>
+        <v>3.2266997</v>
       </c>
       <c r="N20">
-        <v>15.9884046</v>
+        <v>15.7633003</v>
       </c>
       <c r="O20">
-        <v>2.39826069</v>
+        <v>2.364495045</v>
       </c>
       <c r="P20">
-        <v>13.59014391</v>
+        <v>13.398805255</v>
       </c>
       <c r="Q20">
-        <v>17.40014391</v>
+        <v>17.208805255</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1165163072676635</v>
+        <v>0.1172789842521395</v>
       </c>
       <c r="T20">
-        <v>0.9216705460778947</v>
+        <v>0.9316107839087882</v>
       </c>
       <c r="U20">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.15</v>
       </c>
       <c r="W20">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.326635495243631</v>
+        <v>5.885270327449437</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.103926927244233</v>
+        <v>0.103849582528982</v>
       </c>
       <c r="C21">
-        <v>297.4151491841671</v>
+        <v>294.775529477292</v>
       </c>
       <c r="D21">
-        <v>323.7641491841671</v>
+        <v>324.195529477292</v>
       </c>
       <c r="E21">
-        <v>-202.751</v>
+        <v>-199.68</v>
       </c>
       <c r="F21">
-        <v>58.349</v>
+        <v>61.42000000000001</v>
       </c>
       <c r="G21">
         <v>32</v>
@@ -3137,28 +3137,28 @@
         <v>18.99</v>
       </c>
       <c r="M21">
-        <v>3.2266997</v>
+        <v>3.396526000000001</v>
       </c>
       <c r="N21">
-        <v>15.7633003</v>
+        <v>15.593474</v>
       </c>
       <c r="O21">
-        <v>2.364495045</v>
+        <v>2.3390211</v>
       </c>
       <c r="P21">
-        <v>13.398805255</v>
+        <v>13.2544529</v>
       </c>
       <c r="Q21">
-        <v>17.208805255</v>
+        <v>17.0644529</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1172789842521395</v>
+        <v>0.1180607281612275</v>
       </c>
       <c r="T21">
-        <v>0.9316107839087882</v>
+        <v>0.9417995276854541</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.885270327449437</v>
+        <v>5.591006811076965</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.103849582528982</v>
+        <v>0.103772237813731</v>
       </c>
       <c r="C22">
-        <v>294.775529477292</v>
+        <v>292.1370608381416</v>
       </c>
       <c r="D22">
-        <v>324.195529477292</v>
+        <v>324.6280608381416</v>
       </c>
       <c r="E22">
-        <v>-199.68</v>
+        <v>-196.609</v>
       </c>
       <c r="F22">
-        <v>61.42000000000001</v>
+        <v>64.49100000000001</v>
       </c>
       <c r="G22">
         <v>32</v>
@@ -3219,28 +3219,28 @@
         <v>18.99</v>
       </c>
       <c r="M22">
-        <v>3.396526000000001</v>
+        <v>3.566352300000001</v>
       </c>
       <c r="N22">
-        <v>15.593474</v>
+        <v>15.4236477</v>
       </c>
       <c r="O22">
-        <v>2.3390211</v>
+        <v>2.313547155</v>
       </c>
       <c r="P22">
-        <v>13.2544529</v>
+        <v>13.110100545</v>
       </c>
       <c r="Q22">
-        <v>17.0644529</v>
+        <v>16.920100545</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1180607281612275</v>
+        <v>0.1188622630553557</v>
       </c>
       <c r="T22">
-        <v>0.9417995276854541</v>
+        <v>0.952246214342542</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.591006811076965</v>
+        <v>5.324768391501871</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.103772237813731</v>
+        <v>0.10369489309848</v>
       </c>
       <c r="C23">
-        <v>292.1370608381417</v>
+        <v>289.4997478800245</v>
       </c>
       <c r="D23">
-        <v>324.6280608381417</v>
+        <v>325.0617478800245</v>
       </c>
       <c r="E23">
-        <v>-196.609</v>
+        <v>-193.538</v>
       </c>
       <c r="F23">
-        <v>64.491</v>
+        <v>67.56200000000001</v>
       </c>
       <c r="G23">
         <v>32</v>
@@ -3301,28 +3301,28 @@
         <v>18.99</v>
       </c>
       <c r="M23">
-        <v>3.5663523</v>
+        <v>3.736178600000001</v>
       </c>
       <c r="N23">
-        <v>15.4236477</v>
+        <v>15.2538214</v>
       </c>
       <c r="O23">
-        <v>2.313547155</v>
+        <v>2.28807321</v>
       </c>
       <c r="P23">
-        <v>13.110100545</v>
+        <v>12.96574819</v>
       </c>
       <c r="Q23">
-        <v>16.920100545</v>
+        <v>16.77574819</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1188622630553557</v>
+        <v>0.1196843501262564</v>
       </c>
       <c r="T23">
-        <v>0.9522462143425418</v>
+        <v>0.9629607647600679</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.324768391501872</v>
+        <v>5.082733464615423</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.10369489309848</v>
+        <v>0.103617548383229</v>
       </c>
       <c r="C24">
-        <v>289.4997478800245</v>
+        <v>286.8635952409352</v>
       </c>
       <c r="D24">
-        <v>325.0617478800245</v>
+        <v>325.4965952409352</v>
       </c>
       <c r="E24">
-        <v>-193.538</v>
+        <v>-190.467</v>
       </c>
       <c r="F24">
-        <v>67.56200000000001</v>
+        <v>70.63300000000001</v>
       </c>
       <c r="G24">
         <v>32</v>
@@ -3383,28 +3383,28 @@
         <v>18.99</v>
       </c>
       <c r="M24">
-        <v>3.736178600000001</v>
+        <v>3.906004900000001</v>
       </c>
       <c r="N24">
-        <v>15.2538214</v>
+        <v>15.0839951</v>
       </c>
       <c r="O24">
-        <v>2.28807321</v>
+        <v>2.262599265</v>
       </c>
       <c r="P24">
-        <v>12.96574819</v>
+        <v>12.821395835</v>
       </c>
       <c r="Q24">
-        <v>16.77574819</v>
+        <v>16.631395835</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1196843501262564</v>
+        <v>0.1205277901080896</v>
       </c>
       <c r="T24">
-        <v>0.9629607647600679</v>
+        <v>0.9739536151884385</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.082733464615423</v>
+        <v>4.861745053110404</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.103617548383229</v>
+        <v>0.103540203667978</v>
       </c>
       <c r="C25">
-        <v>286.8635952409352</v>
+        <v>284.2286075837189</v>
       </c>
       <c r="D25">
-        <v>325.4965952409352</v>
+        <v>325.9326075837189</v>
       </c>
       <c r="E25">
-        <v>-190.467</v>
+        <v>-187.396</v>
       </c>
       <c r="F25">
-        <v>70.63300000000001</v>
+        <v>73.70400000000001</v>
       </c>
       <c r="G25">
         <v>32</v>
@@ -3465,28 +3465,28 @@
         <v>18.99</v>
       </c>
       <c r="M25">
-        <v>3.906004900000001</v>
+        <v>4.075831200000001</v>
       </c>
       <c r="N25">
-        <v>15.0839951</v>
+        <v>14.9141688</v>
       </c>
       <c r="O25">
-        <v>2.262599265</v>
+        <v>2.23712532</v>
       </c>
       <c r="P25">
-        <v>12.821395835</v>
+        <v>12.67704348</v>
       </c>
       <c r="Q25">
-        <v>16.631395835</v>
+        <v>16.48704348</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1205277901080896</v>
+        <v>0.1213934258789184</v>
       </c>
       <c r="T25">
-        <v>0.9739536151884385</v>
+        <v>0.985235751154398</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.861745053110404</v>
+        <v>4.659172342564138</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.103540203667978</v>
+        <v>0.103994108952727</v>
       </c>
       <c r="C26">
-        <v>284.2286075837189</v>
+        <v>278.6153823358945</v>
       </c>
       <c r="D26">
-        <v>325.9326075837189</v>
+        <v>323.3903823358945</v>
       </c>
       <c r="E26">
-        <v>-187.396</v>
+        <v>-184.325</v>
       </c>
       <c r="F26">
-        <v>73.70400000000001</v>
+        <v>76.77500000000001</v>
       </c>
       <c r="G26">
         <v>32</v>
@@ -3547,45 +3547,45 @@
         <v>18.99</v>
       </c>
       <c r="M26">
-        <v>4.075831200000001</v>
+        <v>4.437595000000001</v>
       </c>
       <c r="N26">
-        <v>14.9141688</v>
+        <v>14.552405</v>
       </c>
       <c r="O26">
-        <v>2.23712532</v>
+        <v>2.18286075</v>
       </c>
       <c r="P26">
-        <v>12.67704348</v>
+        <v>12.36954425</v>
       </c>
       <c r="Q26">
-        <v>16.48704348</v>
+        <v>16.17954425</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1213934258789184</v>
+        <v>0.1222821452703027</v>
       </c>
       <c r="T26">
-        <v>0.985235751154398</v>
+        <v>0.9968187440794496</v>
       </c>
       <c r="U26">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V26">
         <v>0.15</v>
       </c>
       <c r="W26">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.659172342564138</v>
+        <v>4.279345005571711</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.103994108952727</v>
+        <v>0.103938014237476</v>
       </c>
       <c r="C27">
-        <v>278.6153823358945</v>
+        <v>275.8564069492215</v>
       </c>
       <c r="D27">
-        <v>323.3903823358945</v>
+        <v>323.7024069492215</v>
       </c>
       <c r="E27">
-        <v>-184.325</v>
+        <v>-181.254</v>
       </c>
       <c r="F27">
-        <v>76.77500000000001</v>
+        <v>79.846</v>
       </c>
       <c r="G27">
         <v>32</v>
@@ -3629,28 +3629,28 @@
         <v>18.99</v>
       </c>
       <c r="M27">
-        <v>4.437595000000001</v>
+        <v>4.6150988</v>
       </c>
       <c r="N27">
-        <v>14.552405</v>
+        <v>14.3749012</v>
       </c>
       <c r="O27">
-        <v>2.18286075</v>
+        <v>2.15623518</v>
       </c>
       <c r="P27">
-        <v>12.36954425</v>
+        <v>12.21866602</v>
       </c>
       <c r="Q27">
-        <v>16.17954425</v>
+        <v>16.02866602</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1222821452703027</v>
+        <v>0.1231948841046973</v>
       </c>
       <c r="T27">
-        <v>0.9968187440794496</v>
+        <v>1.008714790867341</v>
       </c>
       <c r="U27">
         <v>0.0578</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.279345005571711</v>
+        <v>4.114754813049723</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.103938014237476</v>
+        <v>0.104685169522225</v>
       </c>
       <c r="C28">
-        <v>275.8564069492215</v>
+        <v>268.6781594707743</v>
       </c>
       <c r="D28">
-        <v>323.7024069492215</v>
+        <v>319.5951594707743</v>
       </c>
       <c r="E28">
-        <v>-181.254</v>
+        <v>-178.183</v>
       </c>
       <c r="F28">
-        <v>79.846</v>
+        <v>82.91700000000002</v>
       </c>
       <c r="G28">
         <v>32</v>
@@ -3711,45 +3711,45 @@
         <v>18.99</v>
       </c>
       <c r="M28">
-        <v>4.6150988</v>
+        <v>5.082812100000001</v>
       </c>
       <c r="N28">
-        <v>14.3749012</v>
+        <v>13.9071879</v>
       </c>
       <c r="O28">
-        <v>2.15623518</v>
+        <v>2.086078185</v>
       </c>
       <c r="P28">
-        <v>12.21866602</v>
+        <v>11.821109715</v>
       </c>
       <c r="Q28">
-        <v>16.02866602</v>
+        <v>15.631109715</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1231948841046973</v>
+        <v>0.1241326294825</v>
       </c>
       <c r="T28">
-        <v>1.008714790867341</v>
+        <v>1.020936756745311</v>
       </c>
       <c r="U28">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V28">
         <v>0.15</v>
       </c>
       <c r="W28">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.114754813049723</v>
+        <v>3.736120798169973</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.104685169522225</v>
+        <v>0.104658824806974</v>
       </c>
       <c r="C29">
-        <v>268.6781594707743</v>
+        <v>265.750207577825</v>
       </c>
       <c r="D29">
-        <v>319.5951594707743</v>
+        <v>319.738207577825</v>
       </c>
       <c r="E29">
-        <v>-178.183</v>
+        <v>-175.112</v>
       </c>
       <c r="F29">
-        <v>82.91700000000002</v>
+        <v>85.98800000000001</v>
       </c>
       <c r="G29">
         <v>32</v>
@@ -3793,28 +3793,28 @@
         <v>18.99</v>
       </c>
       <c r="M29">
-        <v>5.082812100000001</v>
+        <v>5.271064400000001</v>
       </c>
       <c r="N29">
-        <v>13.9071879</v>
+        <v>13.7189356</v>
       </c>
       <c r="O29">
-        <v>2.086078185</v>
+        <v>2.05784034</v>
       </c>
       <c r="P29">
-        <v>11.821109715</v>
+        <v>11.66109526</v>
       </c>
       <c r="Q29">
-        <v>15.631109715</v>
+        <v>15.47109526</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1241326294825</v>
+        <v>0.1250964233430195</v>
       </c>
       <c r="T29">
-        <v>1.020936756745311</v>
+        <v>1.033498221675447</v>
       </c>
       <c r="U29">
         <v>0.0613</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.736120798169973</v>
+        <v>3.602687912521046</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.104658824806974</v>
+        <v>0.105322680091723</v>
       </c>
       <c r="C30">
-        <v>265.750207577825</v>
+        <v>259.1131736138028</v>
       </c>
       <c r="D30">
-        <v>319.738207577825</v>
+        <v>316.1721736138028</v>
       </c>
       <c r="E30">
-        <v>-175.112</v>
+        <v>-172.041</v>
       </c>
       <c r="F30">
-        <v>85.98800000000001</v>
+        <v>89.05900000000001</v>
       </c>
       <c r="G30">
         <v>32</v>
@@ -3875,45 +3875,45 @@
         <v>18.99</v>
       </c>
       <c r="M30">
-        <v>5.271064400000001</v>
+        <v>5.708681900000001</v>
       </c>
       <c r="N30">
-        <v>13.7189356</v>
+        <v>13.2813181</v>
       </c>
       <c r="O30">
-        <v>2.05784034</v>
+        <v>1.992197715</v>
       </c>
       <c r="P30">
-        <v>11.66109526</v>
+        <v>11.289120385</v>
       </c>
       <c r="Q30">
-        <v>15.47109526</v>
+        <v>15.099120385</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1250964233430195</v>
+        <v>0.1260873663263704</v>
       </c>
       <c r="T30">
-        <v>1.033498221675447</v>
+        <v>1.046413530688122</v>
       </c>
       <c r="U30">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V30">
         <v>0.15</v>
       </c>
       <c r="W30">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.602687912521046</v>
+        <v>3.326512202405252</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.105322680091723</v>
+        <v>0.105320135376472</v>
       </c>
       <c r="C31">
-        <v>259.1131736138028</v>
+        <v>256.0556911931404</v>
       </c>
       <c r="D31">
-        <v>316.1721736138028</v>
+        <v>316.1856911931404</v>
       </c>
       <c r="E31">
-        <v>-172.041</v>
+        <v>-168.97</v>
       </c>
       <c r="F31">
-        <v>89.059</v>
+        <v>92.13000000000001</v>
       </c>
       <c r="G31">
         <v>32</v>
@@ -3957,28 +3957,28 @@
         <v>18.99</v>
       </c>
       <c r="M31">
-        <v>5.7086819</v>
+        <v>5.905533000000001</v>
       </c>
       <c r="N31">
-        <v>13.2813181</v>
+        <v>13.084467</v>
       </c>
       <c r="O31">
-        <v>1.992197715</v>
+        <v>1.96267005</v>
       </c>
       <c r="P31">
-        <v>11.289120385</v>
+        <v>11.12179695</v>
       </c>
       <c r="Q31">
-        <v>15.099120385</v>
+        <v>14.93179695</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1260873663263704</v>
+        <v>0.1271066219663886</v>
       </c>
       <c r="T31">
-        <v>1.046413530688122</v>
+        <v>1.05969784852973</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.326512202405253</v>
+        <v>3.215628462325077</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.105320135376472</v>
+        <v>0.105317590661221</v>
       </c>
       <c r="C32">
-        <v>256.0556911931404</v>
+        <v>252.9982099283847</v>
       </c>
       <c r="D32">
-        <v>316.1856911931404</v>
+        <v>316.1992099283847</v>
       </c>
       <c r="E32">
-        <v>-168.97</v>
+        <v>-165.899</v>
       </c>
       <c r="F32">
-        <v>92.13000000000001</v>
+        <v>95.20100000000001</v>
       </c>
       <c r="G32">
         <v>32</v>
@@ -4039,28 +4039,28 @@
         <v>18.99</v>
       </c>
       <c r="M32">
-        <v>5.905533000000001</v>
+        <v>6.102384100000001</v>
       </c>
       <c r="N32">
-        <v>13.084467</v>
+        <v>12.8876159</v>
       </c>
       <c r="O32">
-        <v>1.96267005</v>
+        <v>1.933142385</v>
       </c>
       <c r="P32">
-        <v>11.12179695</v>
+        <v>10.954473515</v>
       </c>
       <c r="Q32">
-        <v>14.93179695</v>
+        <v>14.764473515</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1271066219663886</v>
+        <v>0.1281554212481464</v>
       </c>
       <c r="T32">
-        <v>1.05969784852973</v>
+        <v>1.0733672190624</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.215628462325077</v>
+        <v>3.111898511927494</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.105317590661221</v>
+        <v>0.10531504594597</v>
       </c>
       <c r="C33">
-        <v>252.9982099283847</v>
+        <v>249.940729819684</v>
       </c>
       <c r="D33">
-        <v>316.1992099283847</v>
+        <v>316.212729819684</v>
       </c>
       <c r="E33">
-        <v>-165.899</v>
+        <v>-162.828</v>
       </c>
       <c r="F33">
-        <v>95.20100000000001</v>
+        <v>98.27200000000001</v>
       </c>
       <c r="G33">
         <v>32</v>
@@ -4121,28 +4121,28 @@
         <v>18.99</v>
       </c>
       <c r="M33">
-        <v>6.102384100000001</v>
+        <v>6.299235200000001</v>
       </c>
       <c r="N33">
-        <v>12.8876159</v>
+        <v>12.6907648</v>
       </c>
       <c r="O33">
-        <v>1.933142385</v>
+        <v>1.90361472</v>
       </c>
       <c r="P33">
-        <v>10.954473515</v>
+        <v>10.78715008</v>
       </c>
       <c r="Q33">
-        <v>14.764473515</v>
+        <v>14.59715008</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1281554212481464</v>
+        <v>0.1292350675676029</v>
       </c>
       <c r="T33">
-        <v>1.0733672190624</v>
+        <v>1.087438629904854</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.111898511927494</v>
+        <v>3.01465168342976</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.10531504594597</v>
+        <v>0.107500401230719</v>
       </c>
       <c r="C34">
-        <v>249.940729819684</v>
+        <v>235.6698486773827</v>
       </c>
       <c r="D34">
-        <v>316.212729819684</v>
+        <v>305.0128486773827</v>
       </c>
       <c r="E34">
-        <v>-162.828</v>
+        <v>-159.757</v>
       </c>
       <c r="F34">
-        <v>98.27200000000001</v>
+        <v>101.343</v>
       </c>
       <c r="G34">
         <v>32</v>
@@ -4203,45 +4203,45 @@
         <v>18.99</v>
       </c>
       <c r="M34">
-        <v>6.299235200000001</v>
+        <v>7.286561700000002</v>
       </c>
       <c r="N34">
-        <v>12.6907648</v>
+        <v>11.7034383</v>
       </c>
       <c r="O34">
-        <v>1.90361472</v>
+        <v>1.755515745</v>
       </c>
       <c r="P34">
-        <v>10.78715008</v>
+        <v>9.947922555</v>
       </c>
       <c r="Q34">
-        <v>14.59715008</v>
+        <v>13.757922555</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1292350675676029</v>
+        <v>0.1303469421354015</v>
       </c>
       <c r="T34">
-        <v>1.087438629904854</v>
+        <v>1.101930082862008</v>
       </c>
       <c r="U34">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V34">
         <v>0.15</v>
       </c>
       <c r="W34">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.01465168342976</v>
+        <v>2.606167460298868</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.107500401230719</v>
+        <v>0.107564156515468</v>
       </c>
       <c r="C35">
-        <v>235.6698486773827</v>
+        <v>232.2840029461913</v>
       </c>
       <c r="D35">
-        <v>305.0128486773827</v>
+        <v>304.6980029461913</v>
       </c>
       <c r="E35">
-        <v>-159.757</v>
+        <v>-156.686</v>
       </c>
       <c r="F35">
-        <v>101.343</v>
+        <v>104.414</v>
       </c>
       <c r="G35">
         <v>32</v>
@@ -4285,28 +4285,28 @@
         <v>18.99</v>
       </c>
       <c r="M35">
-        <v>7.286561700000002</v>
+        <v>7.507366600000002</v>
       </c>
       <c r="N35">
-        <v>11.7034383</v>
+        <v>11.4826334</v>
       </c>
       <c r="O35">
-        <v>1.755515745</v>
+        <v>1.72239501</v>
       </c>
       <c r="P35">
-        <v>9.947922555</v>
+        <v>9.760238390000001</v>
       </c>
       <c r="Q35">
-        <v>13.757922555</v>
+        <v>13.57023839</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1303469421354015</v>
+        <v>0.1314925098719212</v>
       </c>
       <c r="T35">
-        <v>1.101930082862008</v>
+        <v>1.116860670757258</v>
       </c>
       <c r="U35">
         <v>0.07190000000000001</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.606167460298868</v>
+        <v>2.52951547617243</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.107564156515468</v>
+        <v>0.108788161800217</v>
       </c>
       <c r="C36">
-        <v>232.2840029461913</v>
+        <v>223.2920178721784</v>
       </c>
       <c r="D36">
-        <v>304.6980029461913</v>
+        <v>298.7770178721784</v>
       </c>
       <c r="E36">
-        <v>-156.686</v>
+        <v>-153.615</v>
       </c>
       <c r="F36">
-        <v>104.414</v>
+        <v>107.485</v>
       </c>
       <c r="G36">
         <v>32</v>
@@ -4367,45 +4367,45 @@
         <v>18.99</v>
       </c>
       <c r="M36">
-        <v>7.507366600000002</v>
+        <v>8.147363000000002</v>
       </c>
       <c r="N36">
-        <v>11.4826334</v>
+        <v>10.842637</v>
       </c>
       <c r="O36">
-        <v>1.72239501</v>
+        <v>1.62639555</v>
       </c>
       <c r="P36">
-        <v>9.760238390000001</v>
+        <v>9.21624145</v>
       </c>
       <c r="Q36">
-        <v>13.57023839</v>
+        <v>13.02624145</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1314925098719212</v>
+        <v>0.1326733258464877</v>
       </c>
       <c r="T36">
-        <v>1.116860670757258</v>
+        <v>1.132250661356977</v>
       </c>
       <c r="U36">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V36">
         <v>0.15</v>
       </c>
       <c r="W36">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.52951547617243</v>
+        <v>2.330815504353985</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.108788161800217</v>
+        <v>0.108885067084966</v>
       </c>
       <c r="C37">
-        <v>223.2920178721784</v>
+        <v>219.7620650116802</v>
       </c>
       <c r="D37">
-        <v>298.7770178721784</v>
+        <v>298.3180650116802</v>
       </c>
       <c r="E37">
-        <v>-153.615</v>
+        <v>-150.544</v>
       </c>
       <c r="F37">
-        <v>107.485</v>
+        <v>110.556</v>
       </c>
       <c r="G37">
         <v>32</v>
@@ -4449,28 +4449,28 @@
         <v>18.99</v>
       </c>
       <c r="M37">
-        <v>8.147363000000002</v>
+        <v>8.380144800000002</v>
       </c>
       <c r="N37">
-        <v>10.842637</v>
+        <v>10.6098552</v>
       </c>
       <c r="O37">
-        <v>1.62639555</v>
+        <v>1.59147828</v>
       </c>
       <c r="P37">
-        <v>9.21624145</v>
+        <v>9.01837692</v>
       </c>
       <c r="Q37">
-        <v>13.02624145</v>
+        <v>12.82837692</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1326733258464877</v>
+        <v>0.1338910423202594</v>
       </c>
       <c r="T37">
-        <v>1.132250661356977</v>
+        <v>1.148121589162938</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.330815504353985</v>
+        <v>2.266070629233041</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.108885067084966</v>
+        <v>0.108981972369715</v>
       </c>
       <c r="C38">
-        <v>219.7620650116802</v>
+        <v>216.2335199881319</v>
       </c>
       <c r="D38">
-        <v>298.3180650116802</v>
+        <v>297.8605199881319</v>
       </c>
       <c r="E38">
-        <v>-150.544</v>
+        <v>-147.473</v>
       </c>
       <c r="F38">
-        <v>110.556</v>
+        <v>113.627</v>
       </c>
       <c r="G38">
         <v>32</v>
@@ -4531,28 +4531,28 @@
         <v>18.99</v>
       </c>
       <c r="M38">
-        <v>8.3801448</v>
+        <v>8.612926600000002</v>
       </c>
       <c r="N38">
-        <v>10.6098552</v>
+        <v>10.3770734</v>
       </c>
       <c r="O38">
-        <v>1.59147828</v>
+        <v>1.55656101</v>
       </c>
       <c r="P38">
-        <v>9.018376920000001</v>
+        <v>8.820512390000001</v>
       </c>
       <c r="Q38">
-        <v>12.82837692</v>
+        <v>12.63051239</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1338910423202593</v>
+        <v>0.1351474164598651</v>
       </c>
       <c r="T38">
-        <v>1.148121589162937</v>
+        <v>1.164496355946865</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.266070629233042</v>
+        <v>2.204825477091608</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.108981972369715</v>
+        <v>0.109078877654464</v>
       </c>
       <c r="C39">
-        <v>216.2335199881319</v>
+        <v>212.7063763336483</v>
       </c>
       <c r="D39">
-        <v>297.8605199881319</v>
+        <v>297.4043763336483</v>
       </c>
       <c r="E39">
-        <v>-147.473</v>
+        <v>-144.402</v>
       </c>
       <c r="F39">
-        <v>113.627</v>
+        <v>116.698</v>
       </c>
       <c r="G39">
         <v>32</v>
@@ -4613,28 +4613,28 @@
         <v>18.99</v>
       </c>
       <c r="M39">
-        <v>8.612926600000002</v>
+        <v>8.845708400000001</v>
       </c>
       <c r="N39">
-        <v>10.3770734</v>
+        <v>10.1442916</v>
       </c>
       <c r="O39">
-        <v>1.55656101</v>
+        <v>1.52164374</v>
       </c>
       <c r="P39">
-        <v>8.820512390000001</v>
+        <v>8.622647860000001</v>
       </c>
       <c r="Q39">
-        <v>12.63051239</v>
+        <v>12.43264786</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1351474164598651</v>
+        <v>0.1364443187975225</v>
       </c>
       <c r="T39">
-        <v>1.164496355946865</v>
+        <v>1.181399341014145</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.204825477091608</v>
+        <v>2.14680375401025</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.109078877654464</v>
+        <v>0.109175782939213</v>
       </c>
       <c r="C40">
-        <v>212.7063763336483</v>
+        <v>209.1806276199029</v>
       </c>
       <c r="D40">
-        <v>297.4043763336483</v>
+        <v>296.9496276199029</v>
       </c>
       <c r="E40">
-        <v>-144.402</v>
+        <v>-141.331</v>
       </c>
       <c r="F40">
-        <v>116.698</v>
+        <v>119.769</v>
       </c>
       <c r="G40">
         <v>32</v>
@@ -4695,28 +4695,28 @@
         <v>18.99</v>
       </c>
       <c r="M40">
-        <v>8.845708400000001</v>
+        <v>9.078490200000003</v>
       </c>
       <c r="N40">
-        <v>10.1442916</v>
+        <v>9.911509799999999</v>
       </c>
       <c r="O40">
-        <v>1.52164374</v>
+        <v>1.48672647</v>
       </c>
       <c r="P40">
-        <v>8.622647860000001</v>
+        <v>8.42478333</v>
       </c>
       <c r="Q40">
-        <v>12.43264786</v>
+        <v>12.23478333</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1364443187975225</v>
+        <v>0.1377837425232999</v>
       </c>
       <c r="T40">
-        <v>1.181399341014145</v>
+        <v>1.198856522313138</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.14680375401025</v>
+        <v>2.091757503907423</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.109175782939213</v>
+        <v>0.109272688223962</v>
       </c>
       <c r="C41">
-        <v>209.1806276199029</v>
+        <v>205.6562674578269</v>
       </c>
       <c r="D41">
-        <v>296.9496276199029</v>
+        <v>296.4962674578269</v>
       </c>
       <c r="E41">
-        <v>-141.331</v>
+        <v>-138.26</v>
       </c>
       <c r="F41">
-        <v>119.769</v>
+        <v>122.84</v>
       </c>
       <c r="G41">
         <v>32</v>
@@ -4777,28 +4777,28 @@
         <v>18.99</v>
       </c>
       <c r="M41">
-        <v>9.078490200000003</v>
+        <v>9.311272000000002</v>
       </c>
       <c r="N41">
-        <v>9.911509799999999</v>
+        <v>9.678728</v>
       </c>
       <c r="O41">
-        <v>1.48672647</v>
+        <v>1.4518092</v>
       </c>
       <c r="P41">
-        <v>8.42478333</v>
+        <v>8.2269188</v>
       </c>
       <c r="Q41">
-        <v>12.23478333</v>
+        <v>12.0369188</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1377837425232999</v>
+        <v>0.1391678137066033</v>
       </c>
       <c r="T41">
-        <v>1.198856522313138</v>
+        <v>1.216895609655432</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.091757503907423</v>
+        <v>2.039463566309737</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.109272688223962</v>
+        <v>0.114318293508711</v>
       </c>
       <c r="C42">
-        <v>205.6562674578269</v>
+        <v>180.7516365048994</v>
       </c>
       <c r="D42">
-        <v>296.4962674578269</v>
+        <v>274.6626365048994</v>
       </c>
       <c r="E42">
-        <v>-138.26</v>
+        <v>-135.189</v>
       </c>
       <c r="F42">
-        <v>122.84</v>
+        <v>125.911</v>
       </c>
       <c r="G42">
         <v>32</v>
@@ -4859,45 +4859,45 @@
         <v>18.99</v>
       </c>
       <c r="M42">
-        <v>9.311272000000002</v>
+        <v>11.33199</v>
       </c>
       <c r="N42">
-        <v>9.678728</v>
+        <v>7.658010000000001</v>
       </c>
       <c r="O42">
-        <v>1.4518092</v>
+        <v>1.1487015</v>
       </c>
       <c r="P42">
-        <v>8.2269188</v>
+        <v>6.509308500000001</v>
       </c>
       <c r="Q42">
-        <v>12.0369188</v>
+        <v>10.3193085</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1391678137066033</v>
+        <v>0.1405988025571372</v>
       </c>
       <c r="T42">
-        <v>1.216895609655432</v>
+        <v>1.235546191483905</v>
       </c>
       <c r="U42">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V42">
         <v>0.15</v>
       </c>
       <c r="W42">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.039463566309737</v>
+        <v>1.675786865325508</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.114318293508711</v>
+        <v>0.11453589879346</v>
       </c>
       <c r="C43">
-        <v>180.7516365048994</v>
+        <v>176.8111048296659</v>
       </c>
       <c r="D43">
-        <v>274.6626365048994</v>
+        <v>273.7931048296659</v>
       </c>
       <c r="E43">
-        <v>-135.189</v>
+        <v>-132.118</v>
       </c>
       <c r="F43">
-        <v>125.911</v>
+        <v>128.982</v>
       </c>
       <c r="G43">
         <v>32</v>
@@ -4941,28 +4941,28 @@
         <v>18.99</v>
       </c>
       <c r="M43">
-        <v>11.33199</v>
+        <v>11.60838</v>
       </c>
       <c r="N43">
-        <v>7.658010000000001</v>
+        <v>7.38162</v>
       </c>
       <c r="O43">
-        <v>1.1487015</v>
+        <v>1.107243</v>
       </c>
       <c r="P43">
-        <v>6.509308500000001</v>
+        <v>6.274376999999999</v>
       </c>
       <c r="Q43">
-        <v>10.3193085</v>
+        <v>10.084377</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1405988025571372</v>
+        <v>0.1420791358507931</v>
       </c>
       <c r="T43">
-        <v>1.235546191483905</v>
+        <v>1.254839896823705</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.675786865325508</v>
+        <v>1.635887178055853</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.11453589879346</v>
+        <v>0.114753504078209</v>
       </c>
       <c r="C44">
-        <v>176.8111048296659</v>
+        <v>172.8760613363693</v>
       </c>
       <c r="D44">
-        <v>273.7931048296659</v>
+        <v>272.9290613363693</v>
       </c>
       <c r="E44">
-        <v>-132.118</v>
+        <v>-129.047</v>
       </c>
       <c r="F44">
-        <v>128.982</v>
+        <v>132.053</v>
       </c>
       <c r="G44">
         <v>32</v>
@@ -5023,28 +5023,28 @@
         <v>18.99</v>
       </c>
       <c r="M44">
-        <v>11.60838</v>
+        <v>11.88477</v>
       </c>
       <c r="N44">
-        <v>7.381620000000002</v>
+        <v>7.105230000000002</v>
       </c>
       <c r="O44">
-        <v>1.107243</v>
+        <v>1.0657845</v>
       </c>
       <c r="P44">
-        <v>6.274377000000001</v>
+        <v>6.039445500000002</v>
       </c>
       <c r="Q44">
-        <v>10.084377</v>
+        <v>9.849445500000002</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.142079135850793</v>
+        <v>0.1436114106635245</v>
       </c>
       <c r="T44">
-        <v>1.254839896823705</v>
+        <v>1.274810574280691</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.635887178055853</v>
+        <v>1.597843290194089</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.114753504078209</v>
+        <v>0.114971109362958</v>
       </c>
       <c r="C45">
-        <v>172.8760613363693</v>
+        <v>168.9464542292209</v>
       </c>
       <c r="D45">
-        <v>272.9290613363693</v>
+        <v>272.070454229221</v>
       </c>
       <c r="E45">
-        <v>-129.047</v>
+        <v>-125.976</v>
       </c>
       <c r="F45">
-        <v>132.053</v>
+        <v>135.124</v>
       </c>
       <c r="G45">
         <v>32</v>
@@ -5105,28 +5105,28 @@
         <v>18.99</v>
       </c>
       <c r="M45">
-        <v>11.88477</v>
+        <v>12.16116</v>
       </c>
       <c r="N45">
-        <v>7.105230000000002</v>
+        <v>6.82884</v>
       </c>
       <c r="O45">
-        <v>1.0657845</v>
+        <v>1.024326</v>
       </c>
       <c r="P45">
-        <v>6.039445500000002</v>
+        <v>5.804513999999999</v>
       </c>
       <c r="Q45">
-        <v>9.849445500000002</v>
+        <v>9.614514</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1436114106635245</v>
+        <v>0.1451984095767106</v>
       </c>
       <c r="T45">
-        <v>1.274810574280691</v>
+        <v>1.295494490218283</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.597843290194089</v>
+        <v>1.561528669962405</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.114971109362958</v>
+        <v>0.115188714647707</v>
       </c>
       <c r="C46">
-        <v>168.9464542292209</v>
+        <v>165.0222323621648</v>
       </c>
       <c r="D46">
-        <v>272.070454229221</v>
+        <v>271.2172323621649</v>
       </c>
       <c r="E46">
-        <v>-125.976</v>
+        <v>-122.905</v>
       </c>
       <c r="F46">
-        <v>135.124</v>
+        <v>138.195</v>
       </c>
       <c r="G46">
         <v>32</v>
@@ -5187,28 +5187,28 @@
         <v>18.99</v>
       </c>
       <c r="M46">
-        <v>12.16116</v>
+        <v>12.43755</v>
       </c>
       <c r="N46">
-        <v>6.82884</v>
+        <v>6.55245</v>
       </c>
       <c r="O46">
-        <v>1.024326</v>
+        <v>0.9828675</v>
       </c>
       <c r="P46">
-        <v>5.804513999999999</v>
+        <v>5.5695825</v>
       </c>
       <c r="Q46">
-        <v>9.614514</v>
+        <v>9.3795825</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1451984095767106</v>
+        <v>0.1468431175412854</v>
       </c>
       <c r="T46">
-        <v>1.295494490218283</v>
+        <v>1.316930548553606</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.561528669962405</v>
+        <v>1.526828032852129</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.115188714647707</v>
+        <v>0.1388154246897527</v>
       </c>
       <c r="C47">
-        <v>165.0222323621648</v>
+        <v>93.05974550608258</v>
       </c>
       <c r="D47">
-        <v>271.2172323621649</v>
+        <v>202.3257455060826</v>
       </c>
       <c r="E47">
-        <v>-122.905</v>
+        <v>-119.834</v>
       </c>
       <c r="F47">
-        <v>138.195</v>
+        <v>141.266</v>
       </c>
       <c r="G47">
         <v>32</v>
@@ -5269,45 +5269,45 @@
         <v>18.99</v>
       </c>
       <c r="M47">
-        <v>12.43755</v>
+        <v>20.73784880000001</v>
       </c>
       <c r="N47">
-        <v>6.55245</v>
+        <v>-1.747848800000003</v>
       </c>
       <c r="O47">
-        <v>0.9828675</v>
+        <v>-0.2621773200000005</v>
       </c>
       <c r="P47">
-        <v>5.5695825</v>
+        <v>-1.485671480000003</v>
       </c>
       <c r="Q47">
-        <v>9.3795825</v>
+        <v>2.324328519999997</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1468431175412854</v>
+        <v>0.1491905647950543</v>
       </c>
       <c r="T47">
-        <v>1.316930548553606</v>
+        <v>1.347525655621076</v>
       </c>
       <c r="U47">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.15</v>
+        <v>0.137357545012094</v>
       </c>
       <c r="W47">
-        <v>0.0765</v>
+        <v>0.1266359123922246</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y47">
-        <v>1.526828032852129</v>
+        <v>0.9157169667472933</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1388154246897527</v>
+        <v>0.1398254246897527</v>
       </c>
       <c r="C48">
-        <v>93.05974550608258</v>
+        <v>87.81540777710748</v>
       </c>
       <c r="D48">
-        <v>202.3257455060826</v>
+        <v>200.1524077771075</v>
       </c>
       <c r="E48">
-        <v>-119.834</v>
+        <v>-116.763</v>
       </c>
       <c r="F48">
-        <v>141.266</v>
+        <v>144.337</v>
       </c>
       <c r="G48">
         <v>32</v>
@@ -5351,37 +5351,37 @@
         <v>18.99</v>
       </c>
       <c r="M48">
-        <v>20.73784880000001</v>
+        <v>21.1886716</v>
       </c>
       <c r="N48">
-        <v>-1.747848800000003</v>
+        <v>-2.198671600000001</v>
       </c>
       <c r="O48">
-        <v>-0.2621773200000005</v>
+        <v>-0.3298007400000001</v>
       </c>
       <c r="P48">
-        <v>-1.485671480000003</v>
+        <v>-1.868870860000001</v>
       </c>
       <c r="Q48">
-        <v>2.324328519999997</v>
+        <v>1.941129139999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1491905647950543</v>
+        <v>0.1511413301685459</v>
       </c>
       <c r="T48">
-        <v>1.347525655621076</v>
+        <v>1.372950667991285</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.137357545012094</v>
+        <v>0.1344350440543899</v>
       </c>
       <c r="W48">
-        <v>0.1266359123922246</v>
+        <v>0.1270649355328156</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.9157169667472933</v>
+        <v>0.8962336270292659</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1398254246897527</v>
+        <v>0.1408354246897526</v>
       </c>
       <c r="C49">
-        <v>87.81540777710748</v>
+        <v>82.61726484577625</v>
       </c>
       <c r="D49">
-        <v>200.1524077771075</v>
+        <v>198.0252648457763</v>
       </c>
       <c r="E49">
-        <v>-116.763</v>
+        <v>-113.692</v>
       </c>
       <c r="F49">
-        <v>144.337</v>
+        <v>147.408</v>
       </c>
       <c r="G49">
         <v>32</v>
@@ -5433,37 +5433,37 @@
         <v>18.99</v>
       </c>
       <c r="M49">
-        <v>21.1886716</v>
+        <v>21.6394944</v>
       </c>
       <c r="N49">
-        <v>-2.198671600000001</v>
+        <v>-2.649494400000002</v>
       </c>
       <c r="O49">
-        <v>-0.3298007400000001</v>
+        <v>-0.3974241600000002</v>
       </c>
       <c r="P49">
-        <v>-1.868870860000001</v>
+        <v>-2.252070240000001</v>
       </c>
       <c r="Q49">
-        <v>1.941129139999999</v>
+        <v>1.557929759999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1511413301685459</v>
+        <v>0.1531671249794795</v>
       </c>
       <c r="T49">
-        <v>1.372950667991285</v>
+        <v>1.399353565452656</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.1344350440543899</v>
+        <v>0.1316343139699234</v>
       </c>
       <c r="W49">
-        <v>0.1270649355328156</v>
+        <v>0.1274760827092153</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8962336270292659</v>
+        <v>0.8775620931328229</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1408354246897526</v>
+        <v>0.1418454246897526</v>
       </c>
       <c r="C50">
-        <v>82.61726484577625</v>
+        <v>77.46385937836024</v>
       </c>
       <c r="D50">
-        <v>198.0252648457763</v>
+        <v>195.9428593783603</v>
       </c>
       <c r="E50">
-        <v>-113.692</v>
+        <v>-110.621</v>
       </c>
       <c r="F50">
-        <v>147.408</v>
+        <v>150.479</v>
       </c>
       <c r="G50">
         <v>32</v>
@@ -5515,37 +5515,37 @@
         <v>18.99</v>
       </c>
       <c r="M50">
-        <v>21.6394944</v>
+        <v>22.0903172</v>
       </c>
       <c r="N50">
-        <v>-2.649494400000002</v>
+        <v>-3.100317200000003</v>
       </c>
       <c r="O50">
-        <v>-0.3974241600000002</v>
+        <v>-0.4650475800000004</v>
       </c>
       <c r="P50">
-        <v>-2.252070240000001</v>
+        <v>-2.635269620000003</v>
       </c>
       <c r="Q50">
-        <v>1.557929759999999</v>
+        <v>1.174730379999998</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1531671249794795</v>
+        <v>0.1552723627241751</v>
       </c>
       <c r="T50">
-        <v>1.399353565452655</v>
+        <v>1.426791870657609</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.1316343139699234</v>
+        <v>0.1289478993991086</v>
       </c>
       <c r="W50">
-        <v>0.1274760827092153</v>
+        <v>0.1278704483682108</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8775620931328229</v>
+        <v>0.8596526626607244</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1418454246897526</v>
+        <v>0.1428554246897527</v>
       </c>
       <c r="C51">
-        <v>77.46385937836024</v>
+        <v>72.35379470366777</v>
       </c>
       <c r="D51">
-        <v>195.9428593783603</v>
+        <v>193.9037947036678</v>
       </c>
       <c r="E51">
-        <v>-110.621</v>
+        <v>-107.55</v>
       </c>
       <c r="F51">
-        <v>150.479</v>
+        <v>153.55</v>
       </c>
       <c r="G51">
         <v>32</v>
@@ -5597,37 +5597,37 @@
         <v>18.99</v>
       </c>
       <c r="M51">
-        <v>22.0903172</v>
+        <v>22.54114</v>
       </c>
       <c r="N51">
-        <v>-3.100317200000003</v>
+        <v>-3.55114</v>
       </c>
       <c r="O51">
-        <v>-0.4650475800000004</v>
+        <v>-0.532671</v>
       </c>
       <c r="P51">
-        <v>-2.635269620000003</v>
+        <v>-3.018469</v>
       </c>
       <c r="Q51">
-        <v>1.174730379999998</v>
+        <v>0.791531</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1552723627241751</v>
+        <v>0.1574618099786586</v>
       </c>
       <c r="T51">
-        <v>1.426791870657609</v>
+        <v>1.455327708070762</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.1289478993991086</v>
+        <v>0.1263689414111265</v>
       </c>
       <c r="W51">
-        <v>0.1278704483682108</v>
+        <v>0.1282490394008466</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8596526626607244</v>
+        <v>0.84245960940751</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1428554246897527</v>
+        <v>0.1438654246897526</v>
       </c>
       <c r="C52">
-        <v>72.35379470366777</v>
+        <v>67.28573168915187</v>
       </c>
       <c r="D52">
-        <v>193.9037947036678</v>
+        <v>191.9067316891519</v>
       </c>
       <c r="E52">
-        <v>-107.55</v>
+        <v>-104.479</v>
       </c>
       <c r="F52">
-        <v>153.55</v>
+        <v>156.621</v>
       </c>
       <c r="G52">
         <v>32</v>
@@ -5679,37 +5679,37 @@
         <v>18.99</v>
       </c>
       <c r="M52">
-        <v>22.54114</v>
+        <v>22.9919628</v>
       </c>
       <c r="N52">
-        <v>-3.55114</v>
+        <v>-4.001962800000001</v>
       </c>
       <c r="O52">
-        <v>-0.532671</v>
+        <v>-0.6002944200000001</v>
       </c>
       <c r="P52">
-        <v>-3.018469</v>
+        <v>-3.401668380000001</v>
       </c>
       <c r="Q52">
-        <v>0.791531</v>
+        <v>0.4083316199999989</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1574618099786586</v>
+        <v>0.1597406224272027</v>
       </c>
       <c r="T52">
-        <v>1.455327708070762</v>
+        <v>1.485028273541594</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.1263689414111265</v>
+        <v>0.1238911190305162</v>
       </c>
       <c r="W52">
-        <v>0.1282490394008466</v>
+        <v>0.1286127837263202</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.84245960940751</v>
+        <v>0.8259407935367745</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1438654246897526</v>
+        <v>0.1448754246897526</v>
       </c>
       <c r="C53">
-        <v>67.28573168915187</v>
+        <v>62.25838580809216</v>
       </c>
       <c r="D53">
-        <v>191.9067316891519</v>
+        <v>189.9503858080922</v>
       </c>
       <c r="E53">
-        <v>-104.479</v>
+        <v>-101.408</v>
       </c>
       <c r="F53">
-        <v>156.621</v>
+        <v>159.692</v>
       </c>
       <c r="G53">
         <v>32</v>
@@ -5761,37 +5761,37 @@
         <v>18.99</v>
       </c>
       <c r="M53">
-        <v>22.9919628</v>
+        <v>23.4427856</v>
       </c>
       <c r="N53">
-        <v>-4.001962800000001</v>
+        <v>-4.452785600000002</v>
       </c>
       <c r="O53">
-        <v>-0.6002944200000001</v>
+        <v>-0.6679178400000003</v>
       </c>
       <c r="P53">
-        <v>-3.401668380000001</v>
+        <v>-3.784867760000002</v>
       </c>
       <c r="Q53">
-        <v>0.4083316199999989</v>
+        <v>0.02513223999999825</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1597406224272027</v>
+        <v>0.1621143853944361</v>
       </c>
       <c r="T53">
-        <v>1.485028273541594</v>
+        <v>1.51596636257371</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.1238911190305162</v>
+        <v>0.1215085975106985</v>
       </c>
       <c r="W53">
-        <v>0.1286127837263202</v>
+        <v>0.1289625378854295</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8259407935367745</v>
+        <v>0.8100573167379903</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1448754246897526</v>
+        <v>0.1755180784726826</v>
       </c>
       <c r="C54">
-        <v>62.25838580809216</v>
+        <v>14.31635490180943</v>
       </c>
       <c r="D54">
-        <v>189.9503858080922</v>
+        <v>145.0793549018095</v>
       </c>
       <c r="E54">
-        <v>-101.408</v>
+        <v>-98.33699999999999</v>
       </c>
       <c r="F54">
-        <v>159.692</v>
+        <v>162.763</v>
       </c>
       <c r="G54">
         <v>32</v>
@@ -5843,45 +5843,45 @@
         <v>18.99</v>
       </c>
       <c r="M54">
-        <v>23.4427856</v>
+        <v>32.68281040000001</v>
       </c>
       <c r="N54">
-        <v>-4.452785600000002</v>
+        <v>-13.69281040000001</v>
       </c>
       <c r="O54">
-        <v>-0.6679178400000003</v>
+        <v>-2.053921560000001</v>
       </c>
       <c r="P54">
-        <v>-3.784867760000002</v>
+        <v>-11.63888884000001</v>
       </c>
       <c r="Q54">
-        <v>0.02513223999999825</v>
+        <v>-7.828888840000005</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1621143853944361</v>
+        <v>0.1667437420686367</v>
       </c>
       <c r="T54">
-        <v>1.51596636257371</v>
+        <v>1.576302399037691</v>
       </c>
       <c r="U54">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1215085975106985</v>
+        <v>0.08715590749808956</v>
       </c>
       <c r="W54">
-        <v>0.1289625378854295</v>
+        <v>0.1832990937743836</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.8100573167379903</v>
+        <v>0.5810393833205971</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1755180784726826</v>
+        <v>0.1770680784726826</v>
       </c>
       <c r="C55">
-        <v>14.31635490180943</v>
+        <v>9.532272767034414</v>
       </c>
       <c r="D55">
-        <v>145.0793549018095</v>
+        <v>143.3662727670344</v>
       </c>
       <c r="E55">
-        <v>-98.33699999999999</v>
+        <v>-95.26599999999999</v>
       </c>
       <c r="F55">
-        <v>162.763</v>
+        <v>165.834</v>
       </c>
       <c r="G55">
         <v>32</v>
@@ -5925,37 +5925,37 @@
         <v>18.99</v>
       </c>
       <c r="M55">
-        <v>32.68281040000001</v>
+        <v>33.29946720000001</v>
       </c>
       <c r="N55">
-        <v>-13.69281040000001</v>
+        <v>-14.30946720000001</v>
       </c>
       <c r="O55">
-        <v>-2.053921560000001</v>
+        <v>-2.146420080000001</v>
       </c>
       <c r="P55">
-        <v>-11.63888884000001</v>
+        <v>-12.16304712000001</v>
       </c>
       <c r="Q55">
-        <v>-7.828888840000005</v>
+        <v>-8.353047120000006</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1667437420686367</v>
+        <v>0.1693729538527375</v>
       </c>
       <c r="T55">
-        <v>1.576302399037691</v>
+        <v>1.610569842495032</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.08715590749808956</v>
+        <v>0.0855419092110879</v>
       </c>
       <c r="W55">
-        <v>0.1832990937743836</v>
+        <v>0.1836231846304136</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5810393833205971</v>
+        <v>0.570279394740586</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1770680784726826</v>
+        <v>0.1786180784726826</v>
       </c>
       <c r="C56">
-        <v>9.532272767034414</v>
+        <v>4.788174305256774</v>
       </c>
       <c r="D56">
-        <v>143.3662727670344</v>
+        <v>141.6931743052568</v>
       </c>
       <c r="E56">
-        <v>-95.26599999999999</v>
+        <v>-92.19499999999999</v>
       </c>
       <c r="F56">
-        <v>165.834</v>
+        <v>168.905</v>
       </c>
       <c r="G56">
         <v>32</v>
@@ -6007,37 +6007,37 @@
         <v>18.99</v>
       </c>
       <c r="M56">
-        <v>33.29946720000001</v>
+        <v>33.916124</v>
       </c>
       <c r="N56">
-        <v>-14.30946720000001</v>
+        <v>-14.926124</v>
       </c>
       <c r="O56">
-        <v>-2.146420080000001</v>
+        <v>-2.2389186</v>
       </c>
       <c r="P56">
-        <v>-12.16304712000001</v>
+        <v>-12.6872054</v>
       </c>
       <c r="Q56">
-        <v>-8.353047120000006</v>
+        <v>-8.877205400000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1693729538527375</v>
+        <v>0.1721190194939094</v>
       </c>
       <c r="T56">
-        <v>1.610569842495032</v>
+        <v>1.646360283439366</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.0855419092110879</v>
+        <v>0.08398660177088632</v>
       </c>
       <c r="W56">
-        <v>0.1836231846304136</v>
+        <v>0.183935490364406</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.570279394740586</v>
+        <v>0.5599106784725755</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1786180784726826</v>
+        <v>0.1801680784726826</v>
       </c>
       <c r="C57">
-        <v>4.788174305256774</v>
+        <v>0.08267582414765684</v>
       </c>
       <c r="D57">
-        <v>141.6931743052568</v>
+        <v>140.0586758241477</v>
       </c>
       <c r="E57">
-        <v>-92.19499999999999</v>
+        <v>-89.124</v>
       </c>
       <c r="F57">
-        <v>168.905</v>
+        <v>171.976</v>
       </c>
       <c r="G57">
         <v>32</v>
@@ -6089,37 +6089,37 @@
         <v>18.99</v>
       </c>
       <c r="M57">
-        <v>33.916124</v>
+        <v>34.5327808</v>
       </c>
       <c r="N57">
-        <v>-14.926124</v>
+        <v>-15.5427808</v>
       </c>
       <c r="O57">
-        <v>-2.2389186</v>
+        <v>-2.33141712</v>
       </c>
       <c r="P57">
-        <v>-12.6872054</v>
+        <v>-13.21136368</v>
       </c>
       <c r="Q57">
-        <v>-8.877205400000001</v>
+        <v>-9.401363680000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1721190194939094</v>
+        <v>0.1749899063005892</v>
       </c>
       <c r="T57">
-        <v>1.646360283439366</v>
+        <v>1.683777562608443</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.08398660177088632</v>
+        <v>0.08248684102497762</v>
       </c>
       <c r="W57">
-        <v>0.183935490364406</v>
+        <v>0.1842366423221845</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5599106784725755</v>
+        <v>0.5499122734998509</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1801680784726826</v>
+        <v>0.1817180784726826</v>
       </c>
       <c r="C58">
-        <v>0.08267582414765684</v>
+        <v>-4.585543250510284</v>
       </c>
       <c r="D58">
-        <v>140.0586758241477</v>
+        <v>138.4614567494897</v>
       </c>
       <c r="E58">
-        <v>-89.124</v>
+        <v>-86.053</v>
       </c>
       <c r="F58">
-        <v>171.976</v>
+        <v>175.047</v>
       </c>
       <c r="G58">
         <v>32</v>
@@ -6171,37 +6171,37 @@
         <v>18.99</v>
       </c>
       <c r="M58">
-        <v>34.5327808</v>
+        <v>35.14943760000001</v>
       </c>
       <c r="N58">
-        <v>-15.5427808</v>
+        <v>-16.1594376</v>
       </c>
       <c r="O58">
-        <v>-2.33141712</v>
+        <v>-2.423915640000001</v>
       </c>
       <c r="P58">
-        <v>-13.21136368</v>
+        <v>-13.73552196</v>
       </c>
       <c r="Q58">
-        <v>-9.401363680000001</v>
+        <v>-9.925521960000003</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1749899063005892</v>
+        <v>0.1779943227261843</v>
       </c>
       <c r="T58">
-        <v>1.683777562608443</v>
+        <v>1.722935180343523</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.08248684102497762</v>
+        <v>0.08103970346313592</v>
       </c>
       <c r="W58">
-        <v>0.1842366423221845</v>
+        <v>0.1845272275446023</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5499122734998509</v>
+        <v>0.5402646897542395</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1817180784726826</v>
+        <v>0.1832680784726826</v>
       </c>
       <c r="C59">
-        <v>-4.585543250510284</v>
+        <v>-9.217743933215388</v>
       </c>
       <c r="D59">
-        <v>138.4614567494897</v>
+        <v>136.9002560667846</v>
       </c>
       <c r="E59">
-        <v>-86.053</v>
+        <v>-82.982</v>
       </c>
       <c r="F59">
-        <v>175.047</v>
+        <v>178.118</v>
       </c>
       <c r="G59">
         <v>32</v>
@@ -6253,37 +6253,37 @@
         <v>18.99</v>
       </c>
       <c r="M59">
-        <v>35.14943760000001</v>
+        <v>35.76609440000001</v>
       </c>
       <c r="N59">
-        <v>-16.1594376</v>
+        <v>-16.77609440000001</v>
       </c>
       <c r="O59">
-        <v>-2.423915640000001</v>
+        <v>-2.516414160000001</v>
       </c>
       <c r="P59">
-        <v>-13.73552196</v>
+        <v>-14.25968024000001</v>
       </c>
       <c r="Q59">
-        <v>-9.925521960000003</v>
+        <v>-10.44968024</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1779943227261843</v>
+        <v>0.1811418066006173</v>
       </c>
       <c r="T59">
-        <v>1.722935180343523</v>
+        <v>1.763957446542179</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.08103970346313592</v>
+        <v>0.07964246719653013</v>
       </c>
       <c r="W59">
-        <v>0.1845272275446023</v>
+        <v>0.1848077925869367</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5402646897542395</v>
+        <v>0.5309497813102009</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1832680784726826</v>
+        <v>0.1848180784726826</v>
       </c>
       <c r="C60">
-        <v>-9.21774393321536</v>
+        <v>-13.81513099909046</v>
       </c>
       <c r="D60">
-        <v>136.9002560667846</v>
+        <v>135.3738690009095</v>
       </c>
       <c r="E60">
-        <v>-82.98200000000003</v>
+        <v>-79.91100000000003</v>
       </c>
       <c r="F60">
-        <v>178.118</v>
+        <v>181.189</v>
       </c>
       <c r="G60">
         <v>32</v>
@@ -6335,37 +6335,37 @@
         <v>18.99</v>
       </c>
       <c r="M60">
-        <v>35.7660944</v>
+        <v>36.3827512</v>
       </c>
       <c r="N60">
-        <v>-16.7760944</v>
+        <v>-17.3927512</v>
       </c>
       <c r="O60">
-        <v>-2.51641416</v>
+        <v>-2.60891268</v>
       </c>
       <c r="P60">
-        <v>-14.25968024</v>
+        <v>-14.78383852</v>
       </c>
       <c r="Q60">
-        <v>-10.44968024</v>
+        <v>-10.97383852</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1811418066006173</v>
+        <v>0.184442826273803</v>
       </c>
       <c r="T60">
-        <v>1.763957446542178</v>
+        <v>1.806980798896865</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.07964246719653013</v>
+        <v>0.0782925948711652</v>
       </c>
       <c r="W60">
-        <v>0.1848077925869367</v>
+        <v>0.18507884694987</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5309497813102009</v>
+        <v>0.5219506324744347</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1848180784726826</v>
+        <v>0.1863680784726826</v>
       </c>
       <c r="C61">
-        <v>-13.81513099909046</v>
+        <v>-18.37885608455287</v>
       </c>
       <c r="D61">
-        <v>135.3738690009095</v>
+        <v>133.8811439154472</v>
       </c>
       <c r="E61">
-        <v>-79.91100000000003</v>
+        <v>-76.84</v>
       </c>
       <c r="F61">
-        <v>181.189</v>
+        <v>184.26</v>
       </c>
       <c r="G61">
         <v>32</v>
@@ -6417,37 +6417,37 @@
         <v>18.99</v>
       </c>
       <c r="M61">
-        <v>36.3827512</v>
+        <v>36.999408</v>
       </c>
       <c r="N61">
-        <v>-17.3927512</v>
+        <v>-18.009408</v>
       </c>
       <c r="O61">
-        <v>-2.60891268</v>
+        <v>-2.7014112</v>
       </c>
       <c r="P61">
-        <v>-14.78383852</v>
+        <v>-15.3079968</v>
       </c>
       <c r="Q61">
-        <v>-10.97383852</v>
+        <v>-11.4979968</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.184442826273803</v>
+        <v>0.1879088969306481</v>
       </c>
       <c r="T61">
-        <v>1.806980798896865</v>
+        <v>1.852155318869287</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.0782925948711652</v>
+        <v>0.07698771828997912</v>
       </c>
       <c r="W61">
-        <v>0.18507884694987</v>
+        <v>0.1853408661673722</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5219506324744347</v>
+        <v>0.5132514552665275</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1863680784726826</v>
+        <v>0.1879180784726826</v>
       </c>
       <c r="C62">
-        <v>-18.37885608455287</v>
+        <v>-22.91002058507999</v>
       </c>
       <c r="D62">
-        <v>133.8811439154472</v>
+        <v>132.42097941492</v>
       </c>
       <c r="E62">
-        <v>-76.84</v>
+        <v>-73.76900000000001</v>
       </c>
       <c r="F62">
-        <v>184.26</v>
+        <v>187.331</v>
       </c>
       <c r="G62">
         <v>32</v>
@@ -6499,37 +6499,37 @@
         <v>18.99</v>
       </c>
       <c r="M62">
-        <v>36.999408</v>
+        <v>37.6160648</v>
       </c>
       <c r="N62">
-        <v>-18.009408</v>
+        <v>-18.6260648</v>
       </c>
       <c r="O62">
-        <v>-2.7014112</v>
+        <v>-2.79390972</v>
       </c>
       <c r="P62">
-        <v>-15.3079968</v>
+        <v>-15.83215508</v>
       </c>
       <c r="Q62">
-        <v>-11.4979968</v>
+        <v>-12.02215508</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1879088969306481</v>
+        <v>0.1915527148006647</v>
       </c>
       <c r="T62">
-        <v>1.852155318869287</v>
+        <v>1.899646480891577</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.07698771828997912</v>
+        <v>0.07572562454752045</v>
       </c>
       <c r="W62">
-        <v>0.1853408661673722</v>
+        <v>0.1855942945908579</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5132514552665275</v>
+        <v>0.5048374969834697</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1879180784726826</v>
+        <v>0.2115766965055961</v>
       </c>
       <c r="C63">
-        <v>-22.91002058507999</v>
+        <v>-44.87931834079703</v>
       </c>
       <c r="D63">
-        <v>132.42097941492</v>
+        <v>113.522681659203</v>
       </c>
       <c r="E63">
-        <v>-73.76900000000001</v>
+        <v>-70.69800000000001</v>
       </c>
       <c r="F63">
-        <v>187.331</v>
+        <v>190.402</v>
       </c>
       <c r="G63">
         <v>32</v>
@@ -6581,45 +6581,45 @@
         <v>18.99</v>
       </c>
       <c r="M63">
-        <v>37.6160648</v>
+        <v>44.89679160000001</v>
       </c>
       <c r="N63">
-        <v>-18.6260648</v>
+        <v>-25.90679160000001</v>
       </c>
       <c r="O63">
-        <v>-2.79390972</v>
+        <v>-3.886018740000001</v>
       </c>
       <c r="P63">
-        <v>-15.83215508</v>
+        <v>-22.02077286</v>
       </c>
       <c r="Q63">
-        <v>-12.02215508</v>
+        <v>-18.21077286000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1915527148006647</v>
+        <v>0.1964636231715072</v>
       </c>
       <c r="T63">
-        <v>1.899646480891577</v>
+        <v>1.963652079808965</v>
       </c>
       <c r="U63">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.07572562454752045</v>
+        <v>0.06344551355424694</v>
       </c>
       <c r="W63">
-        <v>0.1855942945908579</v>
+        <v>0.2208395479039086</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.5048374969834697</v>
+        <v>0.4229700903616462</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2115766965055961</v>
+        <v>0.2134766965055961</v>
       </c>
       <c r="C64">
-        <v>-44.87931834079703</v>
+        <v>-49.23668132174521</v>
       </c>
       <c r="D64">
-        <v>113.522681659203</v>
+        <v>112.2363186782548</v>
       </c>
       <c r="E64">
-        <v>-70.69800000000001</v>
+        <v>-67.62700000000001</v>
       </c>
       <c r="F64">
-        <v>190.402</v>
+        <v>193.473</v>
       </c>
       <c r="G64">
         <v>32</v>
@@ -6663,37 +6663,37 @@
         <v>18.99</v>
       </c>
       <c r="M64">
-        <v>44.89679160000001</v>
+        <v>45.62093340000001</v>
       </c>
       <c r="N64">
-        <v>-25.90679160000001</v>
+        <v>-26.6309334</v>
       </c>
       <c r="O64">
-        <v>-3.886018740000001</v>
+        <v>-3.99464001</v>
       </c>
       <c r="P64">
-        <v>-22.02077286</v>
+        <v>-22.63629339</v>
       </c>
       <c r="Q64">
-        <v>-18.21077286000001</v>
+        <v>-18.82629339</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1964636231715072</v>
+        <v>0.2005356129869534</v>
       </c>
       <c r="T64">
-        <v>1.963652079808965</v>
+        <v>2.01672375764164</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.06344551355424694</v>
+        <v>0.06243844191052873</v>
       </c>
       <c r="W64">
-        <v>0.2208395479039086</v>
+        <v>0.2210770153974973</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4229700903616462</v>
+        <v>0.4162562794035248</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2134766965055961</v>
+        <v>0.215376696505596</v>
       </c>
       <c r="C65">
-        <v>-49.23668132174521</v>
+        <v>-53.56521852988186</v>
       </c>
       <c r="D65">
-        <v>112.2363186782548</v>
+        <v>110.9787814701182</v>
       </c>
       <c r="E65">
-        <v>-67.62700000000001</v>
+        <v>-64.55600000000001</v>
       </c>
       <c r="F65">
-        <v>193.473</v>
+        <v>196.544</v>
       </c>
       <c r="G65">
         <v>32</v>
@@ -6745,37 +6745,37 @@
         <v>18.99</v>
       </c>
       <c r="M65">
-        <v>45.62093340000001</v>
+        <v>46.3450752</v>
       </c>
       <c r="N65">
-        <v>-26.6309334</v>
+        <v>-27.3550752</v>
       </c>
       <c r="O65">
-        <v>-3.99464001</v>
+        <v>-4.10326128</v>
       </c>
       <c r="P65">
-        <v>-22.63629339</v>
+        <v>-23.25181392</v>
       </c>
       <c r="Q65">
-        <v>-18.82629339</v>
+        <v>-19.44181392</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2005356129869534</v>
+        <v>0.2048338244588132</v>
       </c>
       <c r="T65">
-        <v>2.01672375764164</v>
+        <v>2.072743862020574</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06243844191052873</v>
+        <v>0.06146284125567671</v>
       </c>
       <c r="W65">
-        <v>0.2210770153974973</v>
+        <v>0.2213070620319114</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4162562794035248</v>
+        <v>0.4097522750378448</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.215376696505596</v>
+        <v>0.2172766965055961</v>
       </c>
       <c r="C66">
-        <v>-53.56521852988186</v>
+        <v>-57.86588815316125</v>
       </c>
       <c r="D66">
-        <v>110.9787814701182</v>
+        <v>109.7491118468388</v>
       </c>
       <c r="E66">
-        <v>-64.55600000000001</v>
+        <v>-61.48500000000001</v>
       </c>
       <c r="F66">
-        <v>196.544</v>
+        <v>199.615</v>
       </c>
       <c r="G66">
         <v>32</v>
@@ -6827,37 +6827,37 @@
         <v>18.99</v>
       </c>
       <c r="M66">
-        <v>46.3450752</v>
+        <v>47.069217</v>
       </c>
       <c r="N66">
-        <v>-27.3550752</v>
+        <v>-28.079217</v>
       </c>
       <c r="O66">
-        <v>-4.10326128</v>
+        <v>-4.211882549999999</v>
       </c>
       <c r="P66">
-        <v>-23.25181392</v>
+        <v>-23.86733445</v>
       </c>
       <c r="Q66">
-        <v>-19.44181392</v>
+        <v>-20.05733445</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2048338244588132</v>
+        <v>0.2093776480147792</v>
       </c>
       <c r="T66">
-        <v>2.072743862020574</v>
+        <v>2.131965115221162</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.06146284125567671</v>
+        <v>0.06051725908251247</v>
       </c>
       <c r="W66">
-        <v>0.2213070620319114</v>
+        <v>0.2215300303083436</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4097522750378448</v>
+        <v>0.4034483938834165</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2172766965055961</v>
+        <v>0.2191766965055961</v>
       </c>
       <c r="C67">
-        <v>-57.86588815316125</v>
+        <v>-62.13960637718895</v>
       </c>
       <c r="D67">
-        <v>109.7491118468388</v>
+        <v>108.5463936228111</v>
       </c>
       <c r="E67">
-        <v>-61.48500000000001</v>
+        <v>-58.41399999999999</v>
       </c>
       <c r="F67">
-        <v>199.615</v>
+        <v>202.686</v>
       </c>
       <c r="G67">
         <v>32</v>
@@ -6909,37 +6909,37 @@
         <v>18.99</v>
       </c>
       <c r="M67">
-        <v>47.069217</v>
+        <v>47.79335880000001</v>
       </c>
       <c r="N67">
-        <v>-28.079217</v>
+        <v>-28.80335880000001</v>
       </c>
       <c r="O67">
-        <v>-4.211882549999999</v>
+        <v>-4.320503820000001</v>
       </c>
       <c r="P67">
-        <v>-23.86733445</v>
+        <v>-24.48285498000001</v>
       </c>
       <c r="Q67">
-        <v>-20.05733445</v>
+        <v>-20.67285498000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2093776480147792</v>
+        <v>0.2141887553093316</v>
       </c>
       <c r="T67">
-        <v>2.131965115221162</v>
+        <v>2.194669971551196</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.06051725908251247</v>
+        <v>0.0596003309145956</v>
       </c>
       <c r="W67">
-        <v>0.2215300303083436</v>
+        <v>0.2217462419703384</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4034483938834165</v>
+        <v>0.3973355394306374</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2191766965055961</v>
+        <v>0.221076696505596</v>
       </c>
       <c r="C68">
-        <v>-62.13960637718895</v>
+        <v>-66.38724966174991</v>
       </c>
       <c r="D68">
-        <v>108.5463936228111</v>
+        <v>107.3697503382501</v>
       </c>
       <c r="E68">
-        <v>-58.41399999999999</v>
+        <v>-55.34299999999999</v>
       </c>
       <c r="F68">
-        <v>202.686</v>
+        <v>205.757</v>
       </c>
       <c r="G68">
         <v>32</v>
@@ -6991,37 +6991,37 @@
         <v>18.99</v>
       </c>
       <c r="M68">
-        <v>47.79335880000001</v>
+        <v>48.51750060000001</v>
       </c>
       <c r="N68">
-        <v>-28.80335880000001</v>
+        <v>-29.52750060000001</v>
       </c>
       <c r="O68">
-        <v>-4.320503820000001</v>
+        <v>-4.429125090000001</v>
       </c>
       <c r="P68">
-        <v>-24.48285498000001</v>
+        <v>-25.09837551000001</v>
       </c>
       <c r="Q68">
-        <v>-20.67285498000001</v>
+        <v>-21.28837551000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2141887553093316</v>
+        <v>0.2192914448641598</v>
       </c>
       <c r="T68">
-        <v>2.194669971551196</v>
+        <v>2.261175122204263</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0596003309145956</v>
+        <v>0.05871077373676581</v>
       </c>
       <c r="W68">
-        <v>0.2217462419703384</v>
+        <v>0.2219559995528706</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3973355394306374</v>
+        <v>0.3914051582451055</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.221076696505596</v>
+        <v>0.2229766965055961</v>
       </c>
       <c r="C69">
-        <v>-66.38724966174991</v>
+        <v>-70.609656870859</v>
       </c>
       <c r="D69">
-        <v>107.3697503382501</v>
+        <v>106.218343129141</v>
       </c>
       <c r="E69">
-        <v>-55.34299999999999</v>
+        <v>-52.27199999999999</v>
       </c>
       <c r="F69">
-        <v>205.757</v>
+        <v>208.828</v>
       </c>
       <c r="G69">
         <v>32</v>
@@ -7073,37 +7073,37 @@
         <v>18.99</v>
       </c>
       <c r="M69">
-        <v>48.51750060000001</v>
+        <v>49.24164240000001</v>
       </c>
       <c r="N69">
-        <v>-29.52750060000001</v>
+        <v>-30.25164240000001</v>
       </c>
       <c r="O69">
-        <v>-4.429125090000001</v>
+        <v>-4.537746360000001</v>
       </c>
       <c r="P69">
-        <v>-25.09837551000001</v>
+        <v>-25.71389604000001</v>
       </c>
       <c r="Q69">
-        <v>-21.28837551000001</v>
+        <v>-21.90389604000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2192914448641598</v>
+        <v>0.2247130525161649</v>
       </c>
       <c r="T69">
-        <v>2.261175122204263</v>
+        <v>2.331836844773147</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05871077373676581</v>
+        <v>0.05784738000534279</v>
       </c>
       <c r="W69">
-        <v>0.2219559995528706</v>
+        <v>0.2221595877947402</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3914051582451055</v>
+        <v>0.3856492000356186</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2229766965055961</v>
+        <v>0.2248766965055961</v>
       </c>
       <c r="C70">
-        <v>-70.609656870859</v>
+        <v>-74.80763126721243</v>
       </c>
       <c r="D70">
-        <v>106.218343129141</v>
+        <v>105.0913687327876</v>
       </c>
       <c r="E70">
-        <v>-52.27199999999999</v>
+        <v>-49.20099999999999</v>
       </c>
       <c r="F70">
-        <v>208.828</v>
+        <v>211.899</v>
       </c>
       <c r="G70">
         <v>32</v>
@@ -7155,37 +7155,37 @@
         <v>18.99</v>
       </c>
       <c r="M70">
-        <v>49.24164240000001</v>
+        <v>49.96578420000001</v>
       </c>
       <c r="N70">
-        <v>-30.25164240000001</v>
+        <v>-30.97578420000001</v>
       </c>
       <c r="O70">
-        <v>-4.537746360000001</v>
+        <v>-4.646367630000001</v>
       </c>
       <c r="P70">
-        <v>-25.71389604000001</v>
+        <v>-26.32941657000001</v>
       </c>
       <c r="Q70">
-        <v>-21.90389604000001</v>
+        <v>-22.51941657000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2247130525161649</v>
+        <v>0.2304844413070088</v>
       </c>
       <c r="T70">
-        <v>2.331836844773147</v>
+        <v>2.407057388152925</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05784738000534279</v>
+        <v>0.0570090121791784</v>
       </c>
       <c r="W70">
-        <v>0.2221595877947402</v>
+        <v>0.2223572749281497</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3856492000356186</v>
+        <v>0.3800600811945227</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2248766965055961</v>
+        <v>0.2267766965055961</v>
       </c>
       <c r="C71">
-        <v>-74.80763126721243</v>
+        <v>-78.98194238100615</v>
       </c>
       <c r="D71">
-        <v>105.0913687327876</v>
+        <v>103.9880576189939</v>
       </c>
       <c r="E71">
-        <v>-49.20099999999999</v>
+        <v>-46.13</v>
       </c>
       <c r="F71">
-        <v>211.899</v>
+        <v>214.97</v>
       </c>
       <c r="G71">
         <v>32</v>
@@ -7237,37 +7237,37 @@
         <v>18.99</v>
       </c>
       <c r="M71">
-        <v>49.96578420000001</v>
+        <v>50.68992600000001</v>
       </c>
       <c r="N71">
-        <v>-30.97578420000001</v>
+        <v>-31.699926</v>
       </c>
       <c r="O71">
-        <v>-4.646367630000001</v>
+        <v>-4.754988900000001</v>
       </c>
       <c r="P71">
-        <v>-26.32941657000001</v>
+        <v>-26.9449371</v>
       </c>
       <c r="Q71">
-        <v>-22.51941657000001</v>
+        <v>-23.13493710000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2304844413070088</v>
+        <v>0.2366405893505758</v>
       </c>
       <c r="T71">
-        <v>2.407057388152925</v>
+        <v>2.487292634424689</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0570090121791784</v>
+        <v>0.05619459771947585</v>
       </c>
       <c r="W71">
-        <v>0.2223572749281497</v>
+        <v>0.2225493138577476</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3800600811945227</v>
+        <v>0.3746306514631724</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2267766965055961</v>
+        <v>0.2286766965055961</v>
       </c>
       <c r="C72">
-        <v>-78.98194238100615</v>
+        <v>-83.13332776225698</v>
       </c>
       <c r="D72">
-        <v>103.9880576189939</v>
+        <v>102.907672237743</v>
       </c>
       <c r="E72">
-        <v>-46.13</v>
+        <v>-43.059</v>
       </c>
       <c r="F72">
-        <v>214.97</v>
+        <v>218.041</v>
       </c>
       <c r="G72">
         <v>32</v>
@@ -7319,37 +7319,37 @@
         <v>18.99</v>
       </c>
       <c r="M72">
-        <v>50.68992600000001</v>
+        <v>51.41406780000001</v>
       </c>
       <c r="N72">
-        <v>-31.699926</v>
+        <v>-32.4240678</v>
       </c>
       <c r="O72">
-        <v>-4.754988900000001</v>
+        <v>-4.86361017</v>
       </c>
       <c r="P72">
-        <v>-26.9449371</v>
+        <v>-27.56045763</v>
       </c>
       <c r="Q72">
-        <v>-23.13493710000001</v>
+        <v>-23.75045763</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2366405893505758</v>
+        <v>0.2432212993281819</v>
       </c>
       <c r="T72">
-        <v>2.487292634424689</v>
+        <v>2.573061345956575</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05619459771947585</v>
+        <v>0.05540312451215929</v>
       </c>
       <c r="W72">
-        <v>0.2225493138577476</v>
+        <v>0.2227359432400328</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3746306514631724</v>
+        <v>0.3693541634143953</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.228676696505596</v>
+        <v>0.230576696505596</v>
       </c>
       <c r="C73">
-        <v>-83.13332776225695</v>
+        <v>-87.26249462501275</v>
       </c>
       <c r="D73">
-        <v>102.9076722377431</v>
+        <v>101.8495053749872</v>
       </c>
       <c r="E73">
-        <v>-43.05900000000003</v>
+        <v>-39.98800000000003</v>
       </c>
       <c r="F73">
-        <v>218.041</v>
+        <v>221.112</v>
       </c>
       <c r="G73">
         <v>32</v>
@@ -7401,37 +7401,37 @@
         <v>18.99</v>
       </c>
       <c r="M73">
-        <v>51.4140678</v>
+        <v>52.1382096</v>
       </c>
       <c r="N73">
-        <v>-32.4240678</v>
+        <v>-33.1482096</v>
       </c>
       <c r="O73">
-        <v>-4.863610169999999</v>
+        <v>-4.97223144</v>
       </c>
       <c r="P73">
-        <v>-27.56045762999999</v>
+        <v>-28.17597816</v>
       </c>
       <c r="Q73">
-        <v>-23.75045763</v>
+        <v>-24.36597816</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2432212993281818</v>
+        <v>0.250272060018474</v>
       </c>
       <c r="T73">
-        <v>2.573061345956575</v>
+        <v>2.664956394026452</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05540312451215931</v>
+        <v>0.05463363667171264</v>
       </c>
       <c r="W73">
-        <v>0.2227359432400328</v>
+        <v>0.2229173884728102</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3693541634143953</v>
+        <v>0.3642242444780843</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.230576696505596</v>
+        <v>0.232476696505596</v>
       </c>
       <c r="C74">
-        <v>-87.26249462501275</v>
+        <v>-91.37012139115376</v>
       </c>
       <c r="D74">
-        <v>101.8495053749872</v>
+        <v>100.8128786088463</v>
       </c>
       <c r="E74">
-        <v>-39.98800000000003</v>
+        <v>-36.917</v>
       </c>
       <c r="F74">
-        <v>221.112</v>
+        <v>224.183</v>
       </c>
       <c r="G74">
         <v>32</v>
@@ -7483,37 +7483,37 @@
         <v>18.99</v>
       </c>
       <c r="M74">
-        <v>52.1382096</v>
+        <v>52.86235140000001</v>
       </c>
       <c r="N74">
-        <v>-33.1482096</v>
+        <v>-33.87235140000001</v>
       </c>
       <c r="O74">
-        <v>-4.97223144</v>
+        <v>-5.080852710000001</v>
       </c>
       <c r="P74">
-        <v>-28.17597816</v>
+        <v>-28.79149869</v>
       </c>
       <c r="Q74">
-        <v>-24.36597816</v>
+        <v>-24.98149869000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.250272060018474</v>
+        <v>0.2578450992784175</v>
       </c>
       <c r="T74">
-        <v>2.664956394026452</v>
+        <v>2.763658482694098</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05463363667171264</v>
+        <v>0.05388523068990835</v>
       </c>
       <c r="W74">
-        <v>0.2229173884728102</v>
+        <v>0.2230938626033196</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3642242444780843</v>
+        <v>0.3592348712660557</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.232476696505596</v>
+        <v>0.234376696505596</v>
       </c>
       <c r="C75">
-        <v>-91.37012139115376</v>
+        <v>-95.45685914086624</v>
       </c>
       <c r="D75">
-        <v>100.8128786088463</v>
+        <v>99.79714085913378</v>
       </c>
       <c r="E75">
-        <v>-36.917</v>
+        <v>-33.846</v>
       </c>
       <c r="F75">
-        <v>224.183</v>
+        <v>227.254</v>
       </c>
       <c r="G75">
         <v>32</v>
@@ -7565,37 +7565,37 @@
         <v>18.99</v>
       </c>
       <c r="M75">
-        <v>52.86235140000001</v>
+        <v>53.58649320000001</v>
       </c>
       <c r="N75">
-        <v>-33.87235140000001</v>
+        <v>-34.5964932</v>
       </c>
       <c r="O75">
-        <v>-5.080852710000001</v>
+        <v>-5.189473980000001</v>
       </c>
       <c r="P75">
-        <v>-28.79149869</v>
+        <v>-29.40701922</v>
       </c>
       <c r="Q75">
-        <v>-24.98149869000001</v>
+        <v>-25.59701922</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2578450992784175</v>
+        <v>0.2660006800198951</v>
       </c>
       <c r="T75">
-        <v>2.763658482694098</v>
+        <v>2.869953039720794</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05388523068990835</v>
+        <v>0.05315705189680148</v>
       </c>
       <c r="W75">
-        <v>0.2230938626033196</v>
+        <v>0.2232655671627342</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3592348712660557</v>
+        <v>0.3543803459786766</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.234376696505596</v>
+        <v>0.236276696505596</v>
       </c>
       <c r="C76">
-        <v>-95.45685914086624</v>
+        <v>-99.52333297630614</v>
       </c>
       <c r="D76">
-        <v>99.79714085913378</v>
+        <v>98.80166702369387</v>
       </c>
       <c r="E76">
-        <v>-33.846</v>
+        <v>-30.77500000000001</v>
       </c>
       <c r="F76">
-        <v>227.254</v>
+        <v>230.325</v>
       </c>
       <c r="G76">
         <v>32</v>
@@ -7647,37 +7647,37 @@
         <v>18.99</v>
       </c>
       <c r="M76">
-        <v>53.58649320000001</v>
+        <v>54.310635</v>
       </c>
       <c r="N76">
-        <v>-34.5964932</v>
+        <v>-35.320635</v>
       </c>
       <c r="O76">
-        <v>-5.189473980000001</v>
+        <v>-5.29809525</v>
       </c>
       <c r="P76">
-        <v>-29.40701922</v>
+        <v>-30.02253975</v>
       </c>
       <c r="Q76">
-        <v>-25.59701922</v>
+        <v>-26.21253975</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2660006800198951</v>
+        <v>0.2748087072206909</v>
       </c>
       <c r="T76">
-        <v>2.869953039720794</v>
+        <v>2.984751161309627</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05315705189680148</v>
+        <v>0.05244829120484414</v>
       </c>
       <c r="W76">
-        <v>0.2232655671627342</v>
+        <v>0.2234326929338978</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3543803459786766</v>
+        <v>0.3496552746989608</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.236276696505596</v>
+        <v>0.238176696505596</v>
       </c>
       <c r="C77">
-        <v>-99.52333297630614</v>
+        <v>-103.5701433044535</v>
       </c>
       <c r="D77">
-        <v>98.80166702369387</v>
+        <v>97.82585669554655</v>
       </c>
       <c r="E77">
-        <v>-30.77500000000001</v>
+        <v>-27.70400000000001</v>
       </c>
       <c r="F77">
-        <v>230.325</v>
+        <v>233.396</v>
       </c>
       <c r="G77">
         <v>32</v>
@@ -7729,37 +7729,37 @@
         <v>18.99</v>
       </c>
       <c r="M77">
-        <v>54.310635</v>
+        <v>55.0347768</v>
       </c>
       <c r="N77">
-        <v>-35.320635</v>
+        <v>-36.0447768</v>
       </c>
       <c r="O77">
-        <v>-5.29809525</v>
+        <v>-5.40671652</v>
       </c>
       <c r="P77">
-        <v>-30.02253975</v>
+        <v>-30.63806028</v>
       </c>
       <c r="Q77">
-        <v>-26.21253975</v>
+        <v>-26.82806028</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2748087072206909</v>
+        <v>0.2843507366882198</v>
       </c>
       <c r="T77">
-        <v>2.984751161309627</v>
+        <v>3.109115793030861</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05244829120484414</v>
+        <v>0.05175818211004355</v>
       </c>
       <c r="W77">
-        <v>0.2234326929338978</v>
+        <v>0.2235954206584517</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3496552746989608</v>
+        <v>0.3450545474002904</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.238176696505596</v>
+        <v>0.2400766965055961</v>
       </c>
       <c r="C78">
-        <v>-103.5701433044535</v>
+        <v>-107.5978670446895</v>
       </c>
       <c r="D78">
-        <v>97.82585669554655</v>
+        <v>96.86913295531048</v>
       </c>
       <c r="E78">
-        <v>-27.70400000000001</v>
+        <v>-24.63300000000001</v>
       </c>
       <c r="F78">
-        <v>233.396</v>
+        <v>236.467</v>
       </c>
       <c r="G78">
         <v>32</v>
@@ -7811,37 +7811,37 @@
         <v>18.99</v>
       </c>
       <c r="M78">
-        <v>55.0347768</v>
+        <v>55.75891860000001</v>
       </c>
       <c r="N78">
-        <v>-36.0447768</v>
+        <v>-36.76891860000001</v>
       </c>
       <c r="O78">
-        <v>-5.40671652</v>
+        <v>-5.515337790000001</v>
       </c>
       <c r="P78">
-        <v>-30.63806028</v>
+        <v>-31.25358081000001</v>
       </c>
       <c r="Q78">
-        <v>-26.82806028</v>
+        <v>-27.44358081000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2843507366882198</v>
+        <v>0.2947225078485771</v>
       </c>
       <c r="T78">
-        <v>3.109115793030861</v>
+        <v>3.244294740553943</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05175818211004355</v>
+        <v>0.05108599792679623</v>
       </c>
       <c r="W78">
-        <v>0.2235954206584517</v>
+        <v>0.2237539216888615</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3450545474002904</v>
+        <v>0.3405733195119749</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2400766965055961</v>
+        <v>0.241976696505596</v>
       </c>
       <c r="C79">
-        <v>-107.5978670446895</v>
+        <v>-111.6070587662013</v>
       </c>
       <c r="D79">
-        <v>96.86913295531048</v>
+        <v>95.93094123379869</v>
       </c>
       <c r="E79">
-        <v>-24.63300000000001</v>
+        <v>-21.56199999999998</v>
       </c>
       <c r="F79">
-        <v>236.467</v>
+        <v>239.538</v>
       </c>
       <c r="G79">
         <v>32</v>
@@ -7893,37 +7893,37 @@
         <v>18.99</v>
       </c>
       <c r="M79">
-        <v>55.75891860000001</v>
+        <v>56.48306040000001</v>
       </c>
       <c r="N79">
-        <v>-36.76891860000001</v>
+        <v>-37.49306040000001</v>
       </c>
       <c r="O79">
-        <v>-5.515337790000001</v>
+        <v>-5.623959060000002</v>
       </c>
       <c r="P79">
-        <v>-31.25358081000001</v>
+        <v>-31.86910134000001</v>
       </c>
       <c r="Q79">
-        <v>-27.44358081000001</v>
+        <v>-28.05910134000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2947225078485771</v>
+        <v>0.3060371672962396</v>
       </c>
       <c r="T79">
-        <v>3.244294740553943</v>
+        <v>3.391762683306394</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05108599792679623</v>
+        <v>0.05043104923542704</v>
       </c>
       <c r="W79">
-        <v>0.2237539216888615</v>
+        <v>0.2239083585902863</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3405733195119749</v>
+        <v>0.336206994902847</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.241976696505596</v>
+        <v>0.2438766965055961</v>
       </c>
       <c r="C80">
-        <v>-111.6070587662013</v>
+        <v>-115.5982517599243</v>
       </c>
       <c r="D80">
-        <v>95.93094123379869</v>
+        <v>95.01074824007578</v>
       </c>
       <c r="E80">
-        <v>-21.56199999999998</v>
+        <v>-18.49099999999999</v>
       </c>
       <c r="F80">
-        <v>239.538</v>
+        <v>242.609</v>
       </c>
       <c r="G80">
         <v>32</v>
@@ -7975,37 +7975,37 @@
         <v>18.99</v>
       </c>
       <c r="M80">
-        <v>56.48306040000001</v>
+        <v>57.20720220000001</v>
       </c>
       <c r="N80">
-        <v>-37.49306040000001</v>
+        <v>-38.21720220000001</v>
       </c>
       <c r="O80">
-        <v>-5.623959060000002</v>
+        <v>-5.732580330000001</v>
       </c>
       <c r="P80">
-        <v>-31.86910134000001</v>
+        <v>-32.48462187000001</v>
       </c>
       <c r="Q80">
-        <v>-28.05910134000001</v>
+        <v>-28.67462187000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3060371672962396</v>
+        <v>0.3184294133579655</v>
       </c>
       <c r="T80">
-        <v>3.391762683306394</v>
+        <v>3.553275192035271</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05043104923542704</v>
+        <v>0.0497926815235862</v>
       </c>
       <c r="W80">
-        <v>0.2239083585902863</v>
+        <v>0.2240588856967384</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.336206994902847</v>
+        <v>0.3319512101572413</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2438766965055961</v>
+        <v>0.2457766965055961</v>
       </c>
       <c r="C81">
-        <v>-115.5982517599243</v>
+        <v>-119.5719590493763</v>
       </c>
       <c r="D81">
-        <v>95.01074824007578</v>
+        <v>94.10804095062375</v>
       </c>
       <c r="E81">
-        <v>-18.49099999999999</v>
+        <v>-15.41999999999999</v>
       </c>
       <c r="F81">
-        <v>242.609</v>
+        <v>245.68</v>
       </c>
       <c r="G81">
         <v>32</v>
@@ -8057,37 +8057,37 @@
         <v>18.99</v>
       </c>
       <c r="M81">
-        <v>57.20720220000001</v>
+        <v>57.93134400000001</v>
       </c>
       <c r="N81">
-        <v>-38.21720220000001</v>
+        <v>-38.94134400000001</v>
       </c>
       <c r="O81">
-        <v>-5.732580330000001</v>
+        <v>-5.841201600000001</v>
       </c>
       <c r="P81">
-        <v>-32.48462187000001</v>
+        <v>-33.10014240000001</v>
       </c>
       <c r="Q81">
-        <v>-28.67462187000001</v>
+        <v>-29.29014240000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3184294133579655</v>
+        <v>0.3320608840258637</v>
       </c>
       <c r="T81">
-        <v>3.553275192035271</v>
+        <v>3.730938951637034</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.0497926815235862</v>
+        <v>0.04917027300454137</v>
       </c>
       <c r="W81">
-        <v>0.2240588856967384</v>
+        <v>0.2242056496255292</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3319512101572413</v>
+        <v>0.3278018200302758</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2457766965055961</v>
+        <v>0.247676696505596</v>
       </c>
       <c r="C82">
-        <v>-119.5719590493763</v>
+        <v>-123.5286743444115</v>
       </c>
       <c r="D82">
-        <v>94.10804095062375</v>
+        <v>93.22232565558853</v>
       </c>
       <c r="E82">
-        <v>-15.41999999999999</v>
+        <v>-12.34899999999999</v>
       </c>
       <c r="F82">
-        <v>245.68</v>
+        <v>248.751</v>
       </c>
       <c r="G82">
         <v>32</v>
@@ -8139,37 +8139,37 @@
         <v>18.99</v>
       </c>
       <c r="M82">
-        <v>57.93134400000001</v>
+        <v>58.65548580000001</v>
       </c>
       <c r="N82">
-        <v>-38.94134400000001</v>
+        <v>-39.66548580000001</v>
       </c>
       <c r="O82">
-        <v>-5.841201600000001</v>
+        <v>-5.949822870000001</v>
       </c>
       <c r="P82">
-        <v>-33.10014240000001</v>
+        <v>-33.71566293000001</v>
       </c>
       <c r="Q82">
-        <v>-29.29014240000001</v>
+        <v>-29.90566293000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3320608840258637</v>
+        <v>0.3471272463430144</v>
       </c>
       <c r="T82">
-        <v>3.730938951637034</v>
+        <v>3.92730415961793</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04917027300454137</v>
+        <v>0.0485632325970779</v>
       </c>
       <c r="W82">
-        <v>0.2242056496255292</v>
+        <v>0.224348789753609</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3278018200302758</v>
+        <v>0.3237548839805193</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.247676696505596</v>
+        <v>0.2495766965055961</v>
       </c>
       <c r="C83">
-        <v>-123.5286743444115</v>
+        <v>-127.4688729416159</v>
       </c>
       <c r="D83">
-        <v>93.22232565558853</v>
+        <v>92.35312705838412</v>
       </c>
       <c r="E83">
-        <v>-12.34899999999999</v>
+        <v>-9.277999999999992</v>
       </c>
       <c r="F83">
-        <v>248.751</v>
+        <v>251.822</v>
       </c>
       <c r="G83">
         <v>32</v>
@@ -8221,37 +8221,37 @@
         <v>18.99</v>
       </c>
       <c r="M83">
-        <v>58.65548580000001</v>
+        <v>59.37962760000001</v>
       </c>
       <c r="N83">
-        <v>-39.66548580000001</v>
+        <v>-40.3896276</v>
       </c>
       <c r="O83">
-        <v>-5.949822870000001</v>
+        <v>-6.058444140000001</v>
       </c>
       <c r="P83">
-        <v>-33.71566293000001</v>
+        <v>-34.33118346000001</v>
       </c>
       <c r="Q83">
-        <v>-29.90566293000001</v>
+        <v>-30.52118346000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3471272463430144</v>
+        <v>0.3638676489176264</v>
       </c>
       <c r="T83">
-        <v>3.92730415961793</v>
+        <v>4.14548772404115</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.0485632325970779</v>
+        <v>0.0479709980532111</v>
       </c>
       <c r="W83">
-        <v>0.224348789753609</v>
+        <v>0.2244884386590528</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3237548839805193</v>
+        <v>0.319806653688074</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2495766965055961</v>
+        <v>0.251476696505596</v>
       </c>
       <c r="C84">
-        <v>-127.4688729416159</v>
+        <v>-131.3930125747982</v>
       </c>
       <c r="D84">
-        <v>92.35312705838412</v>
+        <v>91.49998742520184</v>
       </c>
       <c r="E84">
-        <v>-9.277999999999992</v>
+        <v>-6.206999999999994</v>
       </c>
       <c r="F84">
-        <v>251.822</v>
+        <v>254.893</v>
       </c>
       <c r="G84">
         <v>32</v>
@@ -8303,37 +8303,37 @@
         <v>18.99</v>
       </c>
       <c r="M84">
-        <v>59.37962760000001</v>
+        <v>60.10376940000001</v>
       </c>
       <c r="N84">
-        <v>-40.3896276</v>
+        <v>-41.11376940000001</v>
       </c>
       <c r="O84">
-        <v>-6.058444140000001</v>
+        <v>-6.167065410000001</v>
       </c>
       <c r="P84">
-        <v>-34.33118346000001</v>
+        <v>-34.94670399000001</v>
       </c>
       <c r="Q84">
-        <v>-30.52118346000001</v>
+        <v>-31.13670399000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3638676489176264</v>
+        <v>0.3825775106186632</v>
       </c>
       <c r="T84">
-        <v>4.14548772404115</v>
+        <v>4.389339943102393</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0479709980532111</v>
+        <v>0.04739303422124469</v>
       </c>
       <c r="W84">
-        <v>0.2244884386590528</v>
+        <v>0.2246247225306305</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.319806653688074</v>
+        <v>0.3159535614749647</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.251476696505596</v>
+        <v>0.2533766965055961</v>
       </c>
       <c r="C85">
-        <v>-131.3930125747982</v>
+        <v>-135.3015342187714</v>
       </c>
       <c r="D85">
-        <v>91.49998742520184</v>
+        <v>90.66246578122863</v>
       </c>
       <c r="E85">
-        <v>-6.206999999999994</v>
+        <v>-3.135999999999967</v>
       </c>
       <c r="F85">
-        <v>254.893</v>
+        <v>257.9640000000001</v>
       </c>
       <c r="G85">
         <v>32</v>
@@ -8385,37 +8385,37 @@
         <v>18.99</v>
       </c>
       <c r="M85">
-        <v>60.10376940000001</v>
+        <v>60.82791120000002</v>
       </c>
       <c r="N85">
-        <v>-41.11376940000001</v>
+        <v>-41.83791120000001</v>
       </c>
       <c r="O85">
-        <v>-6.167065410000001</v>
+        <v>-6.275686680000002</v>
       </c>
       <c r="P85">
-        <v>-34.94670399000001</v>
+        <v>-35.56222452000002</v>
       </c>
       <c r="Q85">
-        <v>-31.13670399000001</v>
+        <v>-31.75222452000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3825775106186632</v>
+        <v>0.4036261050323298</v>
       </c>
       <c r="T85">
-        <v>4.389339943102393</v>
+        <v>4.663673689546294</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04739303422124469</v>
+        <v>0.04682883143289654</v>
       </c>
       <c r="W85">
-        <v>0.2246247225306305</v>
+        <v>0.224757761548123</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3159535614749647</v>
+        <v>0.3121922095526436</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2533766965055961</v>
+        <v>0.255276696505596</v>
       </c>
       <c r="C86">
-        <v>-135.3015342187714</v>
+        <v>-139.1948628493918</v>
       </c>
       <c r="D86">
-        <v>90.66246578122863</v>
+        <v>89.84013715060824</v>
       </c>
       <c r="E86">
-        <v>-3.136000000000024</v>
+        <v>-0.06499999999999773</v>
       </c>
       <c r="F86">
-        <v>257.964</v>
+        <v>261.035</v>
       </c>
       <c r="G86">
         <v>32</v>
@@ -8467,37 +8467,37 @@
         <v>18.99</v>
       </c>
       <c r="M86">
-        <v>60.8279112</v>
+        <v>61.55205300000001</v>
       </c>
       <c r="N86">
-        <v>-41.8379112</v>
+        <v>-42.56205300000001</v>
       </c>
       <c r="O86">
-        <v>-6.27568668</v>
+        <v>-6.384307950000001</v>
       </c>
       <c r="P86">
-        <v>-35.56222452</v>
+        <v>-36.17774505000001</v>
       </c>
       <c r="Q86">
-        <v>-31.75222452</v>
+        <v>-32.36774505</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4036261050323295</v>
+        <v>0.4274811787011515</v>
       </c>
       <c r="T86">
-        <v>4.663673689546291</v>
+        <v>4.974585268849378</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04682883143289655</v>
+        <v>0.04627790400427424</v>
       </c>
       <c r="W86">
-        <v>0.224757761548123</v>
+        <v>0.2248876702357921</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3121922095526437</v>
+        <v>0.3085193600284949</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.255276696505596</v>
+        <v>0.257176696505596</v>
       </c>
       <c r="C87">
-        <v>-139.1948628493918</v>
+        <v>-143.0734081626077</v>
       </c>
       <c r="D87">
-        <v>89.84013715060824</v>
+        <v>89.03259183739233</v>
       </c>
       <c r="E87">
-        <v>-0.06499999999999773</v>
+        <v>3.005999999999972</v>
       </c>
       <c r="F87">
-        <v>261.035</v>
+        <v>264.106</v>
       </c>
       <c r="G87">
         <v>32</v>
@@ -8549,37 +8549,37 @@
         <v>18.99</v>
       </c>
       <c r="M87">
-        <v>61.55205300000001</v>
+        <v>62.2761948</v>
       </c>
       <c r="N87">
-        <v>-42.56205300000001</v>
+        <v>-43.2861948</v>
       </c>
       <c r="O87">
-        <v>-6.384307950000001</v>
+        <v>-6.49292922</v>
       </c>
       <c r="P87">
-        <v>-36.17774505000001</v>
+        <v>-36.79326558</v>
       </c>
       <c r="Q87">
-        <v>-32.36774505</v>
+        <v>-32.98326557999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4274811787011515</v>
+        <v>0.4547441200369481</v>
       </c>
       <c r="T87">
-        <v>4.974585268849378</v>
+        <v>5.329912788052905</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04627790400427424</v>
+        <v>0.04573978884143384</v>
       </c>
       <c r="W87">
-        <v>0.2248876702357921</v>
+        <v>0.2250145577911899</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3085193600284949</v>
+        <v>0.304931925609559</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.257176696505596</v>
+        <v>0.2590766965055961</v>
       </c>
       <c r="C88">
-        <v>-143.0734081626077</v>
+        <v>-146.9375652550733</v>
       </c>
       <c r="D88">
-        <v>89.03259183739233</v>
+        <v>88.23943474492674</v>
       </c>
       <c r="E88">
-        <v>3.005999999999972</v>
+        <v>6.076999999999998</v>
       </c>
       <c r="F88">
-        <v>264.106</v>
+        <v>267.177</v>
       </c>
       <c r="G88">
         <v>32</v>
@@ -8631,37 +8631,37 @@
         <v>18.99</v>
       </c>
       <c r="M88">
-        <v>62.2761948</v>
+        <v>63.0003366</v>
       </c>
       <c r="N88">
-        <v>-43.2861948</v>
+        <v>-44.0103366</v>
       </c>
       <c r="O88">
-        <v>-6.49292922</v>
+        <v>-6.60155049</v>
       </c>
       <c r="P88">
-        <v>-36.79326558</v>
+        <v>-37.40878611</v>
       </c>
       <c r="Q88">
-        <v>-32.98326557999999</v>
+        <v>-33.59878611</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4547441200369481</v>
+        <v>0.4862013600397901</v>
       </c>
       <c r="T88">
-        <v>5.329912788052905</v>
+        <v>5.739906079441589</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04573978884143384</v>
+        <v>0.04521404414210701</v>
       </c>
       <c r="W88">
-        <v>0.2250145577911899</v>
+        <v>0.2251385283912912</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.304931925609559</v>
+        <v>0.3014269609473801</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2590766965055961</v>
+        <v>0.2609766965055961</v>
       </c>
       <c r="C89">
-        <v>-146.9375652550733</v>
+        <v>-150.7877152687041</v>
       </c>
       <c r="D89">
-        <v>88.23943474492674</v>
+        <v>87.46028473129596</v>
       </c>
       <c r="E89">
-        <v>6.076999999999998</v>
+        <v>9.148000000000025</v>
       </c>
       <c r="F89">
-        <v>267.177</v>
+        <v>270.248</v>
       </c>
       <c r="G89">
         <v>32</v>
@@ -8713,37 +8713,37 @@
         <v>18.99</v>
       </c>
       <c r="M89">
-        <v>63.0003366</v>
+        <v>63.72447840000002</v>
       </c>
       <c r="N89">
-        <v>-44.0103366</v>
+        <v>-44.73447840000001</v>
       </c>
       <c r="O89">
-        <v>-6.60155049</v>
+        <v>-6.710171760000002</v>
       </c>
       <c r="P89">
-        <v>-37.40878611</v>
+        <v>-38.02430664000001</v>
       </c>
       <c r="Q89">
-        <v>-33.59878611</v>
+        <v>-34.21430664000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4862013600397901</v>
+        <v>0.5229014733764394</v>
       </c>
       <c r="T89">
-        <v>5.739906079441589</v>
+        <v>6.218231586061723</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04521404414210701</v>
+        <v>0.0447002481859467</v>
       </c>
       <c r="W89">
-        <v>0.2251385283912912</v>
+        <v>0.2252596814777538</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3014269609473801</v>
+        <v>0.298001654572978</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2609766965055961</v>
+        <v>0.262876696505596</v>
       </c>
       <c r="C90">
-        <v>-150.7877152687041</v>
+        <v>-154.6242260013827</v>
       </c>
       <c r="D90">
-        <v>87.46028473129596</v>
+        <v>86.69477399861731</v>
       </c>
       <c r="E90">
-        <v>9.148000000000025</v>
+        <v>12.21899999999999</v>
       </c>
       <c r="F90">
-        <v>270.248</v>
+        <v>273.319</v>
       </c>
       <c r="G90">
         <v>32</v>
@@ -8795,37 +8795,37 @@
         <v>18.99</v>
       </c>
       <c r="M90">
-        <v>63.72447840000002</v>
+        <v>64.44862020000001</v>
       </c>
       <c r="N90">
-        <v>-44.73447840000001</v>
+        <v>-45.45862020000001</v>
       </c>
       <c r="O90">
-        <v>-6.710171760000002</v>
+        <v>-6.818793030000001</v>
       </c>
       <c r="P90">
-        <v>-38.02430664000001</v>
+        <v>-38.63982717</v>
       </c>
       <c r="Q90">
-        <v>-34.21430664000001</v>
+        <v>-34.82982717</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5229014733764394</v>
+        <v>0.5662743345924794</v>
       </c>
       <c r="T90">
-        <v>6.218231586061723</v>
+        <v>6.783525366612789</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0447002481859467</v>
+        <v>0.04419799820632932</v>
       </c>
       <c r="W90">
-        <v>0.2252596814777538</v>
+        <v>0.2253781120229476</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.298001654572978</v>
+        <v>0.2946533213755288</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.262876696505596</v>
+        <v>0.2647766965055961</v>
       </c>
       <c r="C91">
-        <v>-154.6242260013827</v>
+        <v>-158.4474524858716</v>
       </c>
       <c r="D91">
-        <v>86.69477399861731</v>
+        <v>85.94254751412848</v>
       </c>
       <c r="E91">
-        <v>12.21899999999999</v>
+        <v>15.29000000000002</v>
       </c>
       <c r="F91">
-        <v>273.319</v>
+        <v>276.39</v>
       </c>
       <c r="G91">
         <v>32</v>
@@ -8877,37 +8877,37 @@
         <v>18.99</v>
       </c>
       <c r="M91">
-        <v>64.44862020000001</v>
+        <v>65.17276200000001</v>
       </c>
       <c r="N91">
-        <v>-45.45862020000001</v>
+        <v>-46.182762</v>
       </c>
       <c r="O91">
-        <v>-6.818793030000001</v>
+        <v>-6.927414300000001</v>
       </c>
       <c r="P91">
-        <v>-38.63982717</v>
+        <v>-39.2553477</v>
       </c>
       <c r="Q91">
-        <v>-34.82982717</v>
+        <v>-35.4453477</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5662743345924794</v>
+        <v>0.6183217680517273</v>
       </c>
       <c r="T91">
-        <v>6.783525366612789</v>
+        <v>7.461877903274068</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04419799820632932</v>
+        <v>0.04370690933737011</v>
       </c>
       <c r="W91">
-        <v>0.2253781120229476</v>
+        <v>0.2254939107782482</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2946533213755288</v>
+        <v>0.2913793955824674</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2647766965055961</v>
+        <v>0.2666766965055961</v>
       </c>
       <c r="C92">
-        <v>-158.4474524858716</v>
+        <v>-162.2577375388454</v>
       </c>
       <c r="D92">
-        <v>85.94254751412848</v>
+        <v>85.20326246115461</v>
       </c>
       <c r="E92">
-        <v>15.29000000000002</v>
+        <v>18.36099999999999</v>
       </c>
       <c r="F92">
-        <v>276.39</v>
+        <v>279.461</v>
       </c>
       <c r="G92">
         <v>32</v>
@@ -8959,37 +8959,37 @@
         <v>18.99</v>
       </c>
       <c r="M92">
-        <v>65.17276200000001</v>
+        <v>65.8969038</v>
       </c>
       <c r="N92">
-        <v>-46.182762</v>
+        <v>-46.9069038</v>
       </c>
       <c r="O92">
-        <v>-6.927414300000001</v>
+        <v>-7.03603557</v>
       </c>
       <c r="P92">
-        <v>-39.2553477</v>
+        <v>-39.87086823</v>
       </c>
       <c r="Q92">
-        <v>-35.4453477</v>
+        <v>-36.06086823</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6183217680517273</v>
+        <v>0.6819352978352528</v>
       </c>
       <c r="T92">
-        <v>7.461877903274068</v>
+        <v>8.2909754480823</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04370690933737011</v>
+        <v>0.04322661363036604</v>
       </c>
       <c r="W92">
-        <v>0.2254939107782482</v>
+        <v>0.2256071645059597</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2913793955824674</v>
+        <v>0.2881774242024403</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2666766965055961</v>
+        <v>0.2685766965055961</v>
       </c>
       <c r="C93">
-        <v>-162.2577375388454</v>
+        <v>-166.0554122818302</v>
       </c>
       <c r="D93">
-        <v>85.20326246115461</v>
+        <v>84.47658771816985</v>
       </c>
       <c r="E93">
-        <v>18.36099999999999</v>
+        <v>21.43200000000002</v>
       </c>
       <c r="F93">
-        <v>279.461</v>
+        <v>282.532</v>
       </c>
       <c r="G93">
         <v>32</v>
@@ -9041,37 +9041,37 @@
         <v>18.99</v>
       </c>
       <c r="M93">
-        <v>65.8969038</v>
+        <v>66.62104560000002</v>
       </c>
       <c r="N93">
-        <v>-46.9069038</v>
+        <v>-47.63104560000001</v>
       </c>
       <c r="O93">
-        <v>-7.03603557</v>
+        <v>-7.144656840000002</v>
       </c>
       <c r="P93">
-        <v>-39.87086823</v>
+        <v>-40.48638876000001</v>
       </c>
       <c r="Q93">
-        <v>-36.06086823</v>
+        <v>-36.67638876000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6819352978352528</v>
+        <v>0.7614522100646595</v>
       </c>
       <c r="T93">
-        <v>8.2909754480823</v>
+        <v>9.327347379092588</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04322661363036604</v>
+        <v>0.04275675913438379</v>
       </c>
       <c r="W93">
-        <v>0.2256071645059597</v>
+        <v>0.2257179561961123</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2881774242024403</v>
+        <v>0.285045060895892</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2685766965055961</v>
+        <v>0.270476696505596</v>
       </c>
       <c r="C94">
-        <v>-166.0554122818302</v>
+        <v>-169.8407966357078</v>
       </c>
       <c r="D94">
-        <v>84.47658771816985</v>
+        <v>83.76220336429216</v>
       </c>
       <c r="E94">
-        <v>21.43200000000002</v>
+        <v>24.50299999999999</v>
       </c>
       <c r="F94">
-        <v>282.532</v>
+        <v>285.603</v>
       </c>
       <c r="G94">
         <v>32</v>
@@ -9123,37 +9123,37 @@
         <v>18.99</v>
       </c>
       <c r="M94">
-        <v>66.62104560000002</v>
+        <v>67.3451874</v>
       </c>
       <c r="N94">
-        <v>-47.63104560000001</v>
+        <v>-48.3551874</v>
       </c>
       <c r="O94">
-        <v>-7.144656840000002</v>
+        <v>-7.253278109999999</v>
       </c>
       <c r="P94">
-        <v>-40.48638876000001</v>
+        <v>-41.10190929</v>
       </c>
       <c r="Q94">
-        <v>-36.67638876000001</v>
+        <v>-37.29190929</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7614522100646595</v>
+        <v>0.8636882400738967</v>
       </c>
       <c r="T94">
-        <v>9.327347379092588</v>
+        <v>10.65982557610582</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04275675913438379</v>
+        <v>0.04229700903616462</v>
       </c>
       <c r="W94">
-        <v>0.2257179561961123</v>
+        <v>0.2258263652692724</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.285045060895892</v>
+        <v>0.2819800602410976</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.270476696505596</v>
+        <v>0.272376696505596</v>
       </c>
       <c r="C95">
-        <v>-169.8407966357078</v>
+        <v>-173.6141997903422</v>
       </c>
       <c r="D95">
-        <v>83.76220336429216</v>
+        <v>83.05980020965785</v>
       </c>
       <c r="E95">
-        <v>24.50299999999999</v>
+        <v>27.57400000000001</v>
       </c>
       <c r="F95">
-        <v>285.603</v>
+        <v>288.674</v>
       </c>
       <c r="G95">
         <v>32</v>
@@ -9205,37 +9205,37 @@
         <v>18.99</v>
       </c>
       <c r="M95">
-        <v>67.3451874</v>
+        <v>68.06932920000001</v>
       </c>
       <c r="N95">
-        <v>-48.3551874</v>
+        <v>-49.07932920000001</v>
       </c>
       <c r="O95">
-        <v>-7.253278109999999</v>
+        <v>-7.361899380000001</v>
       </c>
       <c r="P95">
-        <v>-41.10190929</v>
+        <v>-41.71742982000001</v>
       </c>
       <c r="Q95">
-        <v>-37.29190929</v>
+        <v>-37.90742982</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8636882400738967</v>
+        <v>1.00000294675288</v>
       </c>
       <c r="T95">
-        <v>10.65982557610582</v>
+        <v>12.43646317212346</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04229700903616462</v>
+        <v>0.04184704085492882</v>
       </c>
       <c r="W95">
-        <v>0.2258263652692724</v>
+        <v>0.2259324677664078</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2819800602410976</v>
+        <v>0.2789802723661922</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.272376696505596</v>
+        <v>0.2742766965055961</v>
       </c>
       <c r="C96">
-        <v>-173.6141997903422</v>
+        <v>-177.3759206507714</v>
       </c>
       <c r="D96">
-        <v>83.05980020965785</v>
+        <v>82.3690793492287</v>
       </c>
       <c r="E96">
-        <v>27.57400000000001</v>
+        <v>30.64500000000004</v>
       </c>
       <c r="F96">
-        <v>288.674</v>
+        <v>291.7450000000001</v>
       </c>
       <c r="G96">
         <v>32</v>
@@ -9287,37 +9287,37 @@
         <v>18.99</v>
       </c>
       <c r="M96">
-        <v>68.06932920000001</v>
+        <v>68.79347100000001</v>
       </c>
       <c r="N96">
-        <v>-49.07932920000001</v>
+        <v>-49.80347100000001</v>
       </c>
       <c r="O96">
-        <v>-7.361899380000001</v>
+        <v>-7.470520650000001</v>
       </c>
       <c r="P96">
-        <v>-41.71742982000001</v>
+        <v>-42.33295035</v>
       </c>
       <c r="Q96">
-        <v>-37.90742982</v>
+        <v>-38.52295035</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.00000294675288</v>
+        <v>1.190843536103456</v>
       </c>
       <c r="T96">
-        <v>12.43646317212346</v>
+        <v>14.92375580654816</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04184704085492882</v>
+        <v>0.04140654568803484</v>
       </c>
       <c r="W96">
-        <v>0.2259324677664078</v>
+        <v>0.2260363365267614</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2789802723661922</v>
+        <v>0.2760436379202322</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2742766965055961</v>
+        <v>0.2761766965055961</v>
       </c>
       <c r="C97">
-        <v>-177.3759206507714</v>
+        <v>-181.1262482613213</v>
       </c>
       <c r="D97">
-        <v>82.3690793492287</v>
+        <v>81.68975173867878</v>
       </c>
       <c r="E97">
-        <v>30.64500000000004</v>
+        <v>33.71600000000001</v>
       </c>
       <c r="F97">
-        <v>291.7450000000001</v>
+        <v>294.816</v>
       </c>
       <c r="G97">
         <v>32</v>
@@ -9369,37 +9369,37 @@
         <v>18.99</v>
       </c>
       <c r="M97">
-        <v>68.79347100000001</v>
+        <v>69.51761280000001</v>
       </c>
       <c r="N97">
-        <v>-49.80347100000001</v>
+        <v>-50.52761280000001</v>
       </c>
       <c r="O97">
-        <v>-7.470520650000001</v>
+        <v>-7.579141920000001</v>
       </c>
       <c r="P97">
-        <v>-42.33295035</v>
+        <v>-42.94847088000001</v>
       </c>
       <c r="Q97">
-        <v>-38.52295035</v>
+        <v>-39.13847088000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.190843536103456</v>
+        <v>1.477104420129321</v>
       </c>
       <c r="T97">
-        <v>14.92375580654816</v>
+        <v>18.6546947581852</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04140654568803484</v>
+        <v>0.04097522750378448</v>
       </c>
       <c r="W97">
-        <v>0.2260363365267614</v>
+        <v>0.2261380413546076</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2760436379202322</v>
+        <v>0.2731681833585632</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2761766965055961</v>
+        <v>0.2780766965055961</v>
       </c>
       <c r="C98">
-        <v>-181.1262482613213</v>
+        <v>-184.865462208904</v>
       </c>
       <c r="D98">
-        <v>81.68975173867878</v>
+        <v>81.02153779109598</v>
       </c>
       <c r="E98">
-        <v>33.71600000000001</v>
+        <v>36.78699999999998</v>
       </c>
       <c r="F98">
-        <v>294.816</v>
+        <v>297.887</v>
       </c>
       <c r="G98">
         <v>32</v>
@@ -9451,37 +9451,37 @@
         <v>18.99</v>
       </c>
       <c r="M98">
-        <v>69.51761280000001</v>
+        <v>70.24175460000001</v>
       </c>
       <c r="N98">
-        <v>-50.52761280000001</v>
+        <v>-51.25175460000001</v>
       </c>
       <c r="O98">
-        <v>-7.579141920000001</v>
+        <v>-7.68776319</v>
       </c>
       <c r="P98">
-        <v>-42.94847088000001</v>
+        <v>-43.56399141000001</v>
       </c>
       <c r="Q98">
-        <v>-39.13847088000001</v>
+        <v>-39.75399141</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.477104420129317</v>
+        <v>1.954205893505756</v>
       </c>
       <c r="T98">
-        <v>18.65469475818515</v>
+        <v>24.87292634424687</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04097522750378448</v>
+        <v>0.04055280247797226</v>
       </c>
       <c r="W98">
-        <v>0.2261380413546076</v>
+        <v>0.2262376491756942</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2731681833585632</v>
+        <v>0.2703520165198151</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2780766965055961</v>
+        <v>0.279976696505596</v>
       </c>
       <c r="C99">
-        <v>-184.865462208904</v>
+        <v>-188.5938330066828</v>
       </c>
       <c r="D99">
-        <v>81.02153779109598</v>
+        <v>80.36416699331724</v>
       </c>
       <c r="E99">
-        <v>36.78699999999998</v>
+        <v>39.858</v>
       </c>
       <c r="F99">
-        <v>297.887</v>
+        <v>300.958</v>
       </c>
       <c r="G99">
         <v>32</v>
@@ -9533,37 +9533,37 @@
         <v>18.99</v>
       </c>
       <c r="M99">
-        <v>70.24175460000001</v>
+        <v>70.96589640000001</v>
       </c>
       <c r="N99">
-        <v>-51.25175460000001</v>
+        <v>-51.9758964</v>
       </c>
       <c r="O99">
-        <v>-7.68776319</v>
+        <v>-7.796384460000001</v>
       </c>
       <c r="P99">
-        <v>-43.56399141000001</v>
+        <v>-44.17951194</v>
       </c>
       <c r="Q99">
-        <v>-39.75399141</v>
+        <v>-40.36951194</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.954205893505756</v>
+        <v>2.908408840258634</v>
       </c>
       <c r="T99">
-        <v>24.87292634424687</v>
+        <v>37.3093895163703</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04055280247797226</v>
+        <v>0.04013899837105418</v>
       </c>
       <c r="W99">
-        <v>0.2262376491756942</v>
+        <v>0.2263352241841054</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2703520165198151</v>
+        <v>0.2675933224736946</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.279976696505596</v>
+        <v>0.281876696505596</v>
       </c>
       <c r="C100">
-        <v>-188.5938330066828</v>
+        <v>-192.31162245921</v>
       </c>
       <c r="D100">
-        <v>80.36416699331724</v>
+        <v>79.71737754078995</v>
       </c>
       <c r="E100">
-        <v>39.858</v>
+        <v>42.92899999999997</v>
       </c>
       <c r="F100">
-        <v>300.958</v>
+        <v>304.029</v>
       </c>
       <c r="G100">
         <v>32</v>
@@ -9615,37 +9615,37 @@
         <v>18.99</v>
       </c>
       <c r="M100">
-        <v>70.96589640000001</v>
+        <v>71.6900382</v>
       </c>
       <c r="N100">
-        <v>-51.9758964</v>
+        <v>-52.7000382</v>
       </c>
       <c r="O100">
-        <v>-7.796384460000001</v>
+        <v>-7.90500573</v>
       </c>
       <c r="P100">
-        <v>-44.17951194</v>
+        <v>-44.79503247</v>
       </c>
       <c r="Q100">
-        <v>-40.36951194</v>
+        <v>-40.98503247</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.908408840258634</v>
+        <v>5.771017680517268</v>
       </c>
       <c r="T100">
-        <v>37.3093895163703</v>
+        <v>74.6187790327406</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04013899837105418</v>
+        <v>0.03973355394306374</v>
       </c>
       <c r="W100">
-        <v>0.2263352241841054</v>
+        <v>0.2264308279802256</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2675933224736946</v>
+        <v>0.264890359620425</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.281876696505596</v>
-      </c>
-      <c r="C101">
-        <v>-192.31162245921</v>
-      </c>
-      <c r="D101">
-        <v>79.71737754078995</v>
-      </c>
-      <c r="E101">
-        <v>42.92899999999997</v>
-      </c>
-      <c r="F101">
-        <v>304.029</v>
-      </c>
-      <c r="G101">
-        <v>32</v>
-      </c>
-      <c r="H101">
-        <v>46</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>22.8</v>
-      </c>
-      <c r="K101">
-        <v>3.81</v>
-      </c>
-      <c r="L101">
-        <v>18.99</v>
-      </c>
-      <c r="M101">
-        <v>71.6900382</v>
-      </c>
-      <c r="N101">
-        <v>-52.7000382</v>
-      </c>
-      <c r="O101">
-        <v>-7.90500573</v>
-      </c>
-      <c r="P101">
-        <v>-44.79503247</v>
-      </c>
-      <c r="Q101">
-        <v>-40.98503247</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.771017680517268</v>
-      </c>
-      <c r="T101">
-        <v>74.6187790327406</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03973355394306374</v>
-      </c>
-      <c r="W101">
-        <v>0.2264308279802256</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.264890359620425</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
